--- a/.schema/MSY_KBN_VAL.xlsx
+++ b/.schema/MSY_KBN_VAL.xlsx
@@ -1,21 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KTC0966\git\sample\.schema\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_CADC29B6D2FFBA1170FCC293EB9A1CBDD2F7AB07" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="EMARF.MSY_KBN_VAL" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="EMARF.MSY_KBN_VAL" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Titles" vbProcedure="false">'EMARF.MSY_KBN_VAL'!$2:$2</definedName>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'EMARF.MSY_KBN_VAL'!$A$2:$I$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">EMARF.MSY_KBN_VAL!$A$2:$I$24</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">EMARF.MSY_KBN_VAL!$2:$2</definedName>
   </definedNames>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -26,156 +40,136 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="39">
   <si>
-    <t xml:space="preserve">KBN_NM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KBN_VAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KBN_VAL_MEI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HYOJI_ON</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CRITERIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INSERT_TS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INSERT_USER_ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UPDATE_TS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UPDATE_USER_ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHECK_F</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">なし</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">あり</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DELETE_F</t>
-  </si>
-  <si>
-    <t xml:space="preserve">削除</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PULLDOWN_KB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">１</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">２</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">３</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">４</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">５</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">６</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PULLDOWN_SB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RADIO_KB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STATUS_KB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">否認</t>
-  </si>
-  <si>
-    <t xml:space="preserve">登録</t>
-  </si>
-  <si>
-    <t xml:space="preserve">承認</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TSUKA_KB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">円</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ドル</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ユーロ</t>
+    <t>KBN_NM</t>
+  </si>
+  <si>
+    <t>KBN_VAL</t>
+  </si>
+  <si>
+    <t>KBN_VAL_MEI</t>
+  </si>
+  <si>
+    <t>HYOJI_ON</t>
+  </si>
+  <si>
+    <t>CRITERIA</t>
+  </si>
+  <si>
+    <t>INSERT_TS</t>
+  </si>
+  <si>
+    <t>INSERT_USER_ID</t>
+  </si>
+  <si>
+    <t>UPDATE_TS</t>
+  </si>
+  <si>
+    <t>UPDATE_USER_ID</t>
+  </si>
+  <si>
+    <t>CHECK_F</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>なし</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>あり</t>
+  </si>
+  <si>
+    <t>DELETE_F</t>
+  </si>
+  <si>
+    <t>削除</t>
+  </si>
+  <si>
+    <t>PULLDOWN_KB</t>
+  </si>
+  <si>
+    <t>１</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>２</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>３</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>４</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>５</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>６</t>
+  </si>
+  <si>
+    <t>PULLDOWN_SB</t>
+  </si>
+  <si>
+    <t>RADIO_KB</t>
+  </si>
+  <si>
+    <t>STATUS_KB</t>
+  </si>
+  <si>
+    <t>-1</t>
+  </si>
+  <si>
+    <t>否認</t>
+  </si>
+  <si>
+    <t>登録</t>
+  </si>
+  <si>
+    <t>承認</t>
+  </si>
+  <si>
+    <t>TSUKA_KB</t>
+  </si>
+  <si>
+    <t>円</t>
+  </si>
+  <si>
+    <t>ドル</t>
+  </si>
+  <si>
+    <t>ユーロ</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="0"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd\ h:mm:ss.000"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="176" formatCode="yyyy/mm/dd\ h:mm:ss.000"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="游ゴシック"/>
       <family val="2"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
@@ -186,7 +180,7 @@
       <charset val="128"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -198,6 +192,12 @@
       <color rgb="FFC0C0C0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
       <charset val="128"/>
     </font>
   </fonts>
@@ -216,121 +216,66 @@
     </fill>
   </fills>
   <borders count="2">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="21">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+  <cellStyleXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="7">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="7">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
-    <cellStyle name="標準 2" xfId="20"/>
+  <cellStyles count="2">
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="標準 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
   </cellStyles>
-  <dxfs count="4">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF87E7AD"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF000000"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC0C0C0"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -389,64 +334,76 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546a"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="e7e6e6"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472c4"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ed7d31"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a5a5a5"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="ffc000"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5b9bd5"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70ad47"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563c1"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954f72"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -478,7 +435,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -502,7 +459,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -562,36 +519,35 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I1048576"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12.1"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="13.4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="12.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="22.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="19.9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="22.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="20.7"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="10" style="1" width="8.8"/>
+    <col min="1" max="1" width="14.59765625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.09765625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="16.5" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.3984375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="12.5" style="1" customWidth="1"/>
+    <col min="6" max="6" width="22.5" style="1" customWidth="1"/>
+    <col min="7" max="7" width="19.8984375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="22.5" style="1" customWidth="1"/>
+    <col min="9" max="9" width="20.69921875" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:9" ht="13.2" x14ac:dyDescent="0.45"/>
+    <row r="2" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -620,7 +576,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
       <c r="A3" s="3" t="s">
         <v>9</v>
       </c>
@@ -630,20 +586,20 @@
       <c r="C3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="4" t="n">
+      <c r="D3" s="4">
         <v>1</v>
       </c>
       <c r="E3" s="5"/>
       <c r="F3" s="6"/>
-      <c r="G3" s="4" t="n">
+      <c r="G3" s="4">
         <v>0</v>
       </c>
       <c r="H3" s="6"/>
-      <c r="I3" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I3" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
       <c r="A4" s="3" t="s">
         <v>9</v>
       </c>
@@ -653,20 +609,20 @@
       <c r="C4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D4" s="4">
         <v>2</v>
       </c>
       <c r="E4" s="5"/>
       <c r="F4" s="6"/>
-      <c r="G4" s="4" t="n">
+      <c r="G4" s="4">
         <v>0</v>
       </c>
       <c r="H4" s="6"/>
-      <c r="I4" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I4" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
       <c r="A5" s="3" t="s">
         <v>14</v>
       </c>
@@ -676,20 +632,20 @@
       <c r="C5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" s="4">
         <v>1</v>
       </c>
       <c r="E5" s="5"/>
       <c r="F5" s="6"/>
-      <c r="G5" s="4" t="n">
+      <c r="G5" s="4">
         <v>0</v>
       </c>
       <c r="H5" s="6"/>
-      <c r="I5" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I5" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
       <c r="A6" s="3" t="s">
         <v>14</v>
       </c>
@@ -699,20 +655,20 @@
       <c r="C6" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D6" s="4">
         <v>2</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="6"/>
-      <c r="G6" s="4" t="n">
+      <c r="G6" s="4">
         <v>0</v>
       </c>
       <c r="H6" s="6"/>
-      <c r="I6" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I6" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
       <c r="A7" s="3" t="s">
         <v>16</v>
       </c>
@@ -722,20 +678,20 @@
       <c r="C7" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D7" s="4">
         <v>1</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="6"/>
-      <c r="G7" s="4" t="n">
+      <c r="G7" s="4">
         <v>0</v>
       </c>
       <c r="H7" s="6"/>
-      <c r="I7" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I7" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
       <c r="A8" s="3" t="s">
         <v>16</v>
       </c>
@@ -745,20 +701,20 @@
       <c r="C8" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="D8" s="4">
         <v>2</v>
       </c>
       <c r="E8" s="5"/>
       <c r="F8" s="6"/>
-      <c r="G8" s="4" t="n">
+      <c r="G8" s="4">
         <v>0</v>
       </c>
       <c r="H8" s="6"/>
-      <c r="I8" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I8" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
       <c r="A9" s="3" t="s">
         <v>16</v>
       </c>
@@ -768,20 +724,20 @@
       <c r="C9" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="D9" s="4">
         <v>3</v>
       </c>
       <c r="E9" s="5"/>
       <c r="F9" s="6"/>
-      <c r="G9" s="4" t="n">
+      <c r="G9" s="4">
         <v>0</v>
       </c>
       <c r="H9" s="6"/>
-      <c r="I9" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I9" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
       <c r="A10" s="3" t="s">
         <v>16</v>
       </c>
@@ -791,20 +747,20 @@
       <c r="C10" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="4" t="n">
+      <c r="D10" s="4">
         <v>4</v>
       </c>
       <c r="E10" s="5"/>
       <c r="F10" s="6"/>
-      <c r="G10" s="4" t="n">
+      <c r="G10" s="4">
         <v>0</v>
       </c>
       <c r="H10" s="6"/>
-      <c r="I10" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I10" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
       <c r="A11" s="3" t="s">
         <v>16</v>
       </c>
@@ -814,20 +770,20 @@
       <c r="C11" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D11" s="4" t="n">
+      <c r="D11" s="4">
         <v>5</v>
       </c>
       <c r="E11" s="5"/>
       <c r="F11" s="6"/>
-      <c r="G11" s="4" t="n">
+      <c r="G11" s="4">
         <v>0</v>
       </c>
       <c r="H11" s="6"/>
-      <c r="I11" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I11" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
       <c r="A12" s="3" t="s">
         <v>16</v>
       </c>
@@ -837,20 +793,20 @@
       <c r="C12" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="4" t="n">
+      <c r="D12" s="4">
         <v>6</v>
       </c>
       <c r="E12" s="5"/>
       <c r="F12" s="6"/>
-      <c r="G12" s="4" t="n">
+      <c r="G12" s="4">
         <v>0</v>
       </c>
       <c r="H12" s="6"/>
-      <c r="I12" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I12" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
       <c r="A13" s="3" t="s">
         <v>28</v>
       </c>
@@ -860,20 +816,20 @@
       <c r="C13" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="4" t="n">
+      <c r="D13" s="4">
         <v>1</v>
       </c>
       <c r="E13" s="5"/>
       <c r="F13" s="6"/>
-      <c r="G13" s="4" t="n">
+      <c r="G13" s="4">
         <v>0</v>
       </c>
       <c r="H13" s="6"/>
-      <c r="I13" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I13" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
       <c r="A14" s="3" t="s">
         <v>28</v>
       </c>
@@ -883,20 +839,20 @@
       <c r="C14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="4" t="n">
+      <c r="D14" s="4">
         <v>2</v>
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="6"/>
-      <c r="G14" s="4" t="n">
+      <c r="G14" s="4">
         <v>0</v>
       </c>
       <c r="H14" s="6"/>
-      <c r="I14" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I14" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
       <c r="A15" s="3" t="s">
         <v>28</v>
       </c>
@@ -906,20 +862,20 @@
       <c r="C15" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="4" t="n">
+      <c r="D15" s="4">
         <v>3</v>
       </c>
       <c r="E15" s="5"/>
       <c r="F15" s="6"/>
-      <c r="G15" s="4" t="n">
+      <c r="G15" s="4">
         <v>0</v>
       </c>
       <c r="H15" s="6"/>
-      <c r="I15" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I15" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
       <c r="A16" s="3" t="s">
         <v>29</v>
       </c>
@@ -929,20 +885,20 @@
       <c r="C16" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D16" s="4" t="n">
+      <c r="D16" s="4">
         <v>1</v>
       </c>
       <c r="E16" s="5"/>
       <c r="F16" s="6"/>
-      <c r="G16" s="4" t="n">
+      <c r="G16" s="4">
         <v>0</v>
       </c>
       <c r="H16" s="6"/>
-      <c r="I16" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I16" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
       <c r="A17" s="3" t="s">
         <v>29</v>
       </c>
@@ -952,20 +908,20 @@
       <c r="C17" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D17" s="4" t="n">
+      <c r="D17" s="4">
         <v>2</v>
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="6"/>
-      <c r="G17" s="4" t="n">
+      <c r="G17" s="4">
         <v>0</v>
       </c>
       <c r="H17" s="6"/>
-      <c r="I17" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I17" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
       <c r="A18" s="3" t="s">
         <v>29</v>
       </c>
@@ -975,20 +931,20 @@
       <c r="C18" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D18" s="4" t="n">
+      <c r="D18" s="4">
         <v>3</v>
       </c>
       <c r="E18" s="5"/>
       <c r="F18" s="6"/>
-      <c r="G18" s="4" t="n">
+      <c r="G18" s="4">
         <v>0</v>
       </c>
       <c r="H18" s="6"/>
-      <c r="I18" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I18" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
       <c r="A19" s="3" t="s">
         <v>30</v>
       </c>
@@ -1001,15 +957,15 @@
       <c r="D19" s="5"/>
       <c r="E19" s="5"/>
       <c r="F19" s="6"/>
-      <c r="G19" s="4" t="n">
+      <c r="G19" s="4">
         <v>0</v>
       </c>
       <c r="H19" s="6"/>
-      <c r="I19" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I19" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
       <c r="A20" s="3" t="s">
         <v>30</v>
       </c>
@@ -1022,15 +978,15 @@
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
       <c r="F20" s="6"/>
-      <c r="G20" s="4" t="n">
+      <c r="G20" s="4">
         <v>0</v>
       </c>
       <c r="H20" s="6"/>
-      <c r="I20" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I20" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
       <c r="A21" s="3" t="s">
         <v>30</v>
       </c>
@@ -1043,15 +999,15 @@
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
       <c r="F21" s="6"/>
-      <c r="G21" s="4" t="n">
+      <c r="G21" s="4">
         <v>0</v>
       </c>
       <c r="H21" s="6"/>
-      <c r="I21" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I21" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
       <c r="A22" s="3" t="s">
         <v>35</v>
       </c>
@@ -1064,15 +1020,15 @@
       <c r="D22" s="5"/>
       <c r="E22" s="5"/>
       <c r="F22" s="6"/>
-      <c r="G22" s="4" t="n">
+      <c r="G22" s="4">
         <v>0</v>
       </c>
       <c r="H22" s="6"/>
-      <c r="I22" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I22" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
       <c r="A23" s="3" t="s">
         <v>35</v>
       </c>
@@ -1085,15 +1041,15 @@
       <c r="D23" s="5"/>
       <c r="E23" s="5"/>
       <c r="F23" s="6"/>
-      <c r="G23" s="4" t="n">
+      <c r="G23" s="4">
         <v>0</v>
       </c>
       <c r="H23" s="6"/>
-      <c r="I23" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I23" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
       <c r="A24" s="3" t="s">
         <v>35</v>
       </c>
@@ -1106,30 +1062,29 @@
       <c r="D24" s="5"/>
       <c r="E24" s="5"/>
       <c r="F24" s="6"/>
-      <c r="G24" s="4" t="n">
+      <c r="G24" s="4">
         <v>0</v>
       </c>
       <c r="H24" s="6"/>
-      <c r="I24" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="I24" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1048570" ht="13.2" x14ac:dyDescent="0.45"/>
+    <row r="1048571" ht="13.2" x14ac:dyDescent="0.45"/>
+    <row r="1048572" ht="13.2" x14ac:dyDescent="0.45"/>
+    <row r="1048573" ht="13.2" x14ac:dyDescent="0.45"/>
+    <row r="1048574" ht="13.2" x14ac:dyDescent="0.45"/>
+    <row r="1048575" ht="13.2" x14ac:dyDescent="0.45"/>
+    <row r="1048576" ht="13.2" x14ac:dyDescent="0.45"/>
   </sheetData>
-  <autoFilter ref="A2:I24"/>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <autoFilter ref="A2:I24" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <phoneticPr fontId="4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter>
     <oddHeader>&amp;R&amp;D &amp;T</oddHeader>
     <oddFooter>&amp;C&amp;P / &amp;N</oddFooter>
   </headerFooter>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/.schema/MSY_KBN_VAL.xlsx
+++ b/.schema/MSY_KBN_VAL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KTC0966\git\sample\.schema\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_CADC29B6D2FFBA1170FCC293EB9A1CBDD2F7AB07" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEE9EAFD-082D-46CE-93BC-317590C340FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -590,11 +590,17 @@
         <v>1</v>
       </c>
       <c r="E3" s="5"/>
-      <c r="F3" s="6"/>
+      <c r="F3" s="6" t="str">
+        <f ca="1">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/03/10 17:33:27</v>
+      </c>
       <c r="G3" s="4">
         <v>0</v>
       </c>
-      <c r="H3" s="6"/>
+      <c r="H3" s="6" t="str">
+        <f t="shared" ref="H3:H24" ca="1" si="0">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/03/10 17:33:27</v>
+      </c>
       <c r="I3" s="4">
         <v>0</v>
       </c>
@@ -613,11 +619,17 @@
         <v>2</v>
       </c>
       <c r="E4" s="5"/>
-      <c r="F4" s="6"/>
+      <c r="F4" s="6" t="str">
+        <f t="shared" ref="F4:F24" ca="1" si="1">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/03/10 17:33:27</v>
+      </c>
       <c r="G4" s="4">
         <v>0</v>
       </c>
-      <c r="H4" s="6"/>
+      <c r="H4" s="6" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/03/10 17:33:27</v>
+      </c>
       <c r="I4" s="4">
         <v>0</v>
       </c>
@@ -636,11 +648,17 @@
         <v>1</v>
       </c>
       <c r="E5" s="5"/>
-      <c r="F5" s="6"/>
+      <c r="F5" s="6" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>2026/03/10 17:33:27</v>
+      </c>
       <c r="G5" s="4">
         <v>0</v>
       </c>
-      <c r="H5" s="6"/>
+      <c r="H5" s="6" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/03/10 17:33:27</v>
+      </c>
       <c r="I5" s="4">
         <v>0</v>
       </c>
@@ -659,11 +677,17 @@
         <v>2</v>
       </c>
       <c r="E6" s="5"/>
-      <c r="F6" s="6"/>
+      <c r="F6" s="6" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>2026/03/10 17:33:27</v>
+      </c>
       <c r="G6" s="4">
         <v>0</v>
       </c>
-      <c r="H6" s="6"/>
+      <c r="H6" s="6" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/03/10 17:33:27</v>
+      </c>
       <c r="I6" s="4">
         <v>0</v>
       </c>
@@ -682,11 +706,17 @@
         <v>1</v>
       </c>
       <c r="E7" s="5"/>
-      <c r="F7" s="6"/>
+      <c r="F7" s="6" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>2026/03/10 17:33:27</v>
+      </c>
       <c r="G7" s="4">
         <v>0</v>
       </c>
-      <c r="H7" s="6"/>
+      <c r="H7" s="6" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/03/10 17:33:27</v>
+      </c>
       <c r="I7" s="4">
         <v>0</v>
       </c>
@@ -705,11 +735,17 @@
         <v>2</v>
       </c>
       <c r="E8" s="5"/>
-      <c r="F8" s="6"/>
+      <c r="F8" s="6" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>2026/03/10 17:33:27</v>
+      </c>
       <c r="G8" s="4">
         <v>0</v>
       </c>
-      <c r="H8" s="6"/>
+      <c r="H8" s="6" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/03/10 17:33:27</v>
+      </c>
       <c r="I8" s="4">
         <v>0</v>
       </c>
@@ -728,11 +764,17 @@
         <v>3</v>
       </c>
       <c r="E9" s="5"/>
-      <c r="F9" s="6"/>
+      <c r="F9" s="6" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>2026/03/10 17:33:27</v>
+      </c>
       <c r="G9" s="4">
         <v>0</v>
       </c>
-      <c r="H9" s="6"/>
+      <c r="H9" s="6" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/03/10 17:33:27</v>
+      </c>
       <c r="I9" s="4">
         <v>0</v>
       </c>
@@ -751,11 +793,17 @@
         <v>4</v>
       </c>
       <c r="E10" s="5"/>
-      <c r="F10" s="6"/>
+      <c r="F10" s="6" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>2026/03/10 17:33:27</v>
+      </c>
       <c r="G10" s="4">
         <v>0</v>
       </c>
-      <c r="H10" s="6"/>
+      <c r="H10" s="6" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/03/10 17:33:27</v>
+      </c>
       <c r="I10" s="4">
         <v>0</v>
       </c>
@@ -774,11 +822,17 @@
         <v>5</v>
       </c>
       <c r="E11" s="5"/>
-      <c r="F11" s="6"/>
+      <c r="F11" s="6" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>2026/03/10 17:33:27</v>
+      </c>
       <c r="G11" s="4">
         <v>0</v>
       </c>
-      <c r="H11" s="6"/>
+      <c r="H11" s="6" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/03/10 17:33:27</v>
+      </c>
       <c r="I11" s="4">
         <v>0</v>
       </c>
@@ -797,11 +851,17 @@
         <v>6</v>
       </c>
       <c r="E12" s="5"/>
-      <c r="F12" s="6"/>
+      <c r="F12" s="6" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>2026/03/10 17:33:27</v>
+      </c>
       <c r="G12" s="4">
         <v>0</v>
       </c>
-      <c r="H12" s="6"/>
+      <c r="H12" s="6" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/03/10 17:33:27</v>
+      </c>
       <c r="I12" s="4">
         <v>0</v>
       </c>
@@ -820,11 +880,17 @@
         <v>1</v>
       </c>
       <c r="E13" s="5"/>
-      <c r="F13" s="6"/>
+      <c r="F13" s="6" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>2026/03/10 17:33:27</v>
+      </c>
       <c r="G13" s="4">
         <v>0</v>
       </c>
-      <c r="H13" s="6"/>
+      <c r="H13" s="6" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/03/10 17:33:27</v>
+      </c>
       <c r="I13" s="4">
         <v>0</v>
       </c>
@@ -843,11 +909,17 @@
         <v>2</v>
       </c>
       <c r="E14" s="5"/>
-      <c r="F14" s="6"/>
+      <c r="F14" s="6" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>2026/03/10 17:33:27</v>
+      </c>
       <c r="G14" s="4">
         <v>0</v>
       </c>
-      <c r="H14" s="6"/>
+      <c r="H14" s="6" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/03/10 17:33:27</v>
+      </c>
       <c r="I14" s="4">
         <v>0</v>
       </c>
@@ -866,11 +938,17 @@
         <v>3</v>
       </c>
       <c r="E15" s="5"/>
-      <c r="F15" s="6"/>
+      <c r="F15" s="6" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>2026/03/10 17:33:27</v>
+      </c>
       <c r="G15" s="4">
         <v>0</v>
       </c>
-      <c r="H15" s="6"/>
+      <c r="H15" s="6" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/03/10 17:33:27</v>
+      </c>
       <c r="I15" s="4">
         <v>0</v>
       </c>
@@ -889,11 +967,17 @@
         <v>1</v>
       </c>
       <c r="E16" s="5"/>
-      <c r="F16" s="6"/>
+      <c r="F16" s="6" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>2026/03/10 17:33:27</v>
+      </c>
       <c r="G16" s="4">
         <v>0</v>
       </c>
-      <c r="H16" s="6"/>
+      <c r="H16" s="6" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/03/10 17:33:27</v>
+      </c>
       <c r="I16" s="4">
         <v>0</v>
       </c>
@@ -912,11 +996,17 @@
         <v>2</v>
       </c>
       <c r="E17" s="5"/>
-      <c r="F17" s="6"/>
+      <c r="F17" s="6" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>2026/03/10 17:33:27</v>
+      </c>
       <c r="G17" s="4">
         <v>0</v>
       </c>
-      <c r="H17" s="6"/>
+      <c r="H17" s="6" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/03/10 17:33:27</v>
+      </c>
       <c r="I17" s="4">
         <v>0</v>
       </c>
@@ -935,11 +1025,17 @@
         <v>3</v>
       </c>
       <c r="E18" s="5"/>
-      <c r="F18" s="6"/>
+      <c r="F18" s="6" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>2026/03/10 17:33:27</v>
+      </c>
       <c r="G18" s="4">
         <v>0</v>
       </c>
-      <c r="H18" s="6"/>
+      <c r="H18" s="6" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/03/10 17:33:27</v>
+      </c>
       <c r="I18" s="4">
         <v>0</v>
       </c>
@@ -956,11 +1052,17 @@
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="5"/>
-      <c r="F19" s="6"/>
+      <c r="F19" s="6" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>2026/03/10 17:33:27</v>
+      </c>
       <c r="G19" s="4">
         <v>0</v>
       </c>
-      <c r="H19" s="6"/>
+      <c r="H19" s="6" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/03/10 17:33:27</v>
+      </c>
       <c r="I19" s="4">
         <v>0</v>
       </c>
@@ -977,11 +1079,17 @@
       </c>
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
-      <c r="F20" s="6"/>
+      <c r="F20" s="6" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>2026/03/10 17:33:27</v>
+      </c>
       <c r="G20" s="4">
         <v>0</v>
       </c>
-      <c r="H20" s="6"/>
+      <c r="H20" s="6" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/03/10 17:33:27</v>
+      </c>
       <c r="I20" s="4">
         <v>0</v>
       </c>
@@ -998,11 +1106,17 @@
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
-      <c r="F21" s="6"/>
+      <c r="F21" s="6" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>2026/03/10 17:33:27</v>
+      </c>
       <c r="G21" s="4">
         <v>0</v>
       </c>
-      <c r="H21" s="6"/>
+      <c r="H21" s="6" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/03/10 17:33:27</v>
+      </c>
       <c r="I21" s="4">
         <v>0</v>
       </c>
@@ -1019,11 +1133,17 @@
       </c>
       <c r="D22" s="5"/>
       <c r="E22" s="5"/>
-      <c r="F22" s="6"/>
+      <c r="F22" s="6" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>2026/03/10 17:33:27</v>
+      </c>
       <c r="G22" s="4">
         <v>0</v>
       </c>
-      <c r="H22" s="6"/>
+      <c r="H22" s="6" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/03/10 17:33:27</v>
+      </c>
       <c r="I22" s="4">
         <v>0</v>
       </c>
@@ -1040,11 +1160,17 @@
       </c>
       <c r="D23" s="5"/>
       <c r="E23" s="5"/>
-      <c r="F23" s="6"/>
+      <c r="F23" s="6" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>2026/03/10 17:33:27</v>
+      </c>
       <c r="G23" s="4">
         <v>0</v>
       </c>
-      <c r="H23" s="6"/>
+      <c r="H23" s="6" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/03/10 17:33:27</v>
+      </c>
       <c r="I23" s="4">
         <v>0</v>
       </c>
@@ -1061,11 +1187,17 @@
       </c>
       <c r="D24" s="5"/>
       <c r="E24" s="5"/>
-      <c r="F24" s="6"/>
+      <c r="F24" s="6" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>2026/03/10 17:33:27</v>
+      </c>
       <c r="G24" s="4">
         <v>0</v>
       </c>
-      <c r="H24" s="6"/>
+      <c r="H24" s="6" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/03/10 17:33:27</v>
+      </c>
       <c r="I24" s="4">
         <v>0</v>
       </c>

--- a/.schema/MSY_KBN_VAL.xlsx
+++ b/.schema/MSY_KBN_VAL.xlsx
@@ -1,35 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KTC0966\git\sample\.schema\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEE9EAFD-082D-46CE-93BC-317590C340FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="Calc"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="EMARF.MSY_KBN_VAL" sheetId="1" r:id="rId1"/>
+    <sheet name="EMARF.MSY_KBN_VAL" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">EMARF.MSY_KBN_VAL!$A$2:$I$24</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">EMARF.MSY_KBN_VAL!$2:$2</definedName>
+    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Titles" vbProcedure="false">'EMARF.MSY_KBN_VAL'!$2:$2</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'EMARF.MSY_KBN_VAL'!$A$2:$I$24</definedName>
   </definedNames>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -40,136 +26,156 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="39">
   <si>
-    <t>KBN_NM</t>
-  </si>
-  <si>
-    <t>KBN_VAL</t>
-  </si>
-  <si>
-    <t>KBN_VAL_MEI</t>
-  </si>
-  <si>
-    <t>HYOJI_ON</t>
-  </si>
-  <si>
-    <t>CRITERIA</t>
-  </si>
-  <si>
-    <t>INSERT_TS</t>
-  </si>
-  <si>
-    <t>INSERT_USER_ID</t>
-  </si>
-  <si>
-    <t>UPDATE_TS</t>
-  </si>
-  <si>
-    <t>UPDATE_USER_ID</t>
-  </si>
-  <si>
-    <t>CHECK_F</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>なし</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>あり</t>
-  </si>
-  <si>
-    <t>DELETE_F</t>
-  </si>
-  <si>
-    <t>削除</t>
-  </si>
-  <si>
-    <t>PULLDOWN_KB</t>
-  </si>
-  <si>
-    <t>１</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>２</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>３</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>４</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>５</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>６</t>
-  </si>
-  <si>
-    <t>PULLDOWN_SB</t>
-  </si>
-  <si>
-    <t>RADIO_KB</t>
-  </si>
-  <si>
-    <t>STATUS_KB</t>
-  </si>
-  <si>
-    <t>-1</t>
-  </si>
-  <si>
-    <t>否認</t>
-  </si>
-  <si>
-    <t>登録</t>
-  </si>
-  <si>
-    <t>承認</t>
-  </si>
-  <si>
-    <t>TSUKA_KB</t>
-  </si>
-  <si>
-    <t>円</t>
-  </si>
-  <si>
-    <t>ドル</t>
-  </si>
-  <si>
-    <t>ユーロ</t>
+    <t xml:space="preserve">KBN_NM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KBN_VAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KBN_VAL_MEI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HYOJI_ON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRITERIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INSERT_TS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INSERT_USER_ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UPDATE_TS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UPDATE_USER_ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHECK_F</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">なし</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">あり</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DELETE_F</t>
+  </si>
+  <si>
+    <t xml:space="preserve">削除</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PULLDOWN_KB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">１</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">２</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">３</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">４</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">５</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">６</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PULLDOWN_SB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RADIO_KB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STATUS_KB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">否認</t>
+  </si>
+  <si>
+    <t xml:space="preserve">登録</t>
+  </si>
+  <si>
+    <t xml:space="preserve">承認</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TSUKA_KB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">円</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ドル</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ユーロ</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="176" formatCode="yyyy/mm/dd\ h:mm:ss.000"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="0"/>
+    <numFmt numFmtId="166" formatCode="yyyy/mm/dd\ h:mm:ss.000"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="游ゴシック"/>
       <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
@@ -180,7 +186,7 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
+      <b val="true"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -192,12 +198,6 @@
       <color rgb="FFC0C0C0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="3"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="6"/>
-      <name val="游ゴシック"/>
-      <family val="2"/>
       <charset val="128"/>
     </font>
   </fonts>
@@ -216,66 +216,121 @@
     </fill>
   </fills>
   <borders count="2">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
+  <cellStyleXfs count="21">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="7">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
-    <cellStyle name="標準 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
+  <cellStyles count="7">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
+    <cellStyle name="標準 2" xfId="20"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <dxfs count="4">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF87E7AD"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF000000"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC0C0C0"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -334,76 +389,64 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office テーマ">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="44546a"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="e7e6e6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4472c4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="ed7d31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="a5a5a5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="ffc000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="5b9bd5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="70ad47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0563c1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="954f72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -435,7 +478,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -459,7 +502,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -519,35 +562,36 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:I1048576"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="14.59765625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="12.09765625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="16.5" style="1" customWidth="1"/>
-    <col min="4" max="4" width="13.3984375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="12.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="22.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="19.8984375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="22.5" style="1" customWidth="1"/>
-    <col min="9" max="9" width="20.69921875" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.796875" style="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="13.4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="12.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="22.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="19.9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="22.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="20.7"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="10" style="1" width="8.8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="13.2" x14ac:dyDescent="0.45"/>
-    <row r="2" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -576,7 +620,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
         <v>9</v>
       </c>
@@ -586,26 +630,26 @@
       <c r="C3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E3" s="5"/>
       <c r="F3" s="6" t="str">
-        <f ca="1">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
-        <v>2026/03/10 17:33:27</v>
-      </c>
-      <c r="G3" s="4">
+        <f aca="true">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/03/10 20:44:15</v>
+      </c>
+      <c r="G3" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H3" s="6" t="str">
-        <f t="shared" ref="H3:H24" ca="1" si="0">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
-        <v>2026/03/10 17:33:27</v>
-      </c>
-      <c r="I3" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
+        <f aca="true">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/03/10 20:44:15</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
         <v>9</v>
       </c>
@@ -615,26 +659,26 @@
       <c r="C4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="4" t="n">
         <v>2</v>
       </c>
       <c r="E4" s="5"/>
       <c r="F4" s="6" t="str">
-        <f t="shared" ref="F4:F24" ca="1" si="1">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
-        <v>2026/03/10 17:33:27</v>
-      </c>
-      <c r="G4" s="4">
+        <f aca="true">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/03/10 20:44:15</v>
+      </c>
+      <c r="G4" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H4" s="6" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>2026/03/10 17:33:27</v>
-      </c>
-      <c r="I4" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
+        <f aca="true">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/03/10 20:44:15</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
         <v>14</v>
       </c>
@@ -644,26 +688,26 @@
       <c r="C5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E5" s="5"/>
       <c r="F5" s="6" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>2026/03/10 17:33:27</v>
-      </c>
-      <c r="G5" s="4">
+        <f aca="true">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/03/10 20:44:15</v>
+      </c>
+      <c r="G5" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H5" s="6" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>2026/03/10 17:33:27</v>
-      </c>
-      <c r="I5" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
+        <f aca="true">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/03/10 20:44:15</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
         <v>14</v>
       </c>
@@ -673,26 +717,26 @@
       <c r="C6" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="4" t="n">
         <v>2</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="6" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>2026/03/10 17:33:27</v>
-      </c>
-      <c r="G6" s="4">
+        <f aca="true">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/03/10 20:44:15</v>
+      </c>
+      <c r="G6" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H6" s="6" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>2026/03/10 17:33:27</v>
-      </c>
-      <c r="I6" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
+        <f aca="true">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/03/10 20:44:15</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
         <v>16</v>
       </c>
@@ -702,26 +746,26 @@
       <c r="C7" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="6" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>2026/03/10 17:33:27</v>
-      </c>
-      <c r="G7" s="4">
+        <f aca="true">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/03/10 20:44:15</v>
+      </c>
+      <c r="G7" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H7" s="6" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>2026/03/10 17:33:27</v>
-      </c>
-      <c r="I7" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
+        <f aca="true">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/03/10 20:44:15</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
         <v>16</v>
       </c>
@@ -731,26 +775,26 @@
       <c r="C8" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="4" t="n">
         <v>2</v>
       </c>
       <c r="E8" s="5"/>
       <c r="F8" s="6" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>2026/03/10 17:33:27</v>
-      </c>
-      <c r="G8" s="4">
+        <f aca="true">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/03/10 20:44:15</v>
+      </c>
+      <c r="G8" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H8" s="6" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>2026/03/10 17:33:27</v>
-      </c>
-      <c r="I8" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
+        <f aca="true">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/03/10 20:44:15</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
         <v>16</v>
       </c>
@@ -760,26 +804,26 @@
       <c r="C9" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D9" s="4" t="n">
         <v>3</v>
       </c>
       <c r="E9" s="5"/>
       <c r="F9" s="6" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>2026/03/10 17:33:27</v>
-      </c>
-      <c r="G9" s="4">
+        <f aca="true">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/03/10 20:44:15</v>
+      </c>
+      <c r="G9" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H9" s="6" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>2026/03/10 17:33:27</v>
-      </c>
-      <c r="I9" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
+        <f aca="true">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/03/10 20:44:15</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
         <v>16</v>
       </c>
@@ -789,26 +833,26 @@
       <c r="C10" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="4" t="n">
         <v>4</v>
       </c>
       <c r="E10" s="5"/>
       <c r="F10" s="6" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>2026/03/10 17:33:27</v>
-      </c>
-      <c r="G10" s="4">
+        <f aca="true">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/03/10 20:44:15</v>
+      </c>
+      <c r="G10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H10" s="6" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>2026/03/10 17:33:27</v>
-      </c>
-      <c r="I10" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
+        <f aca="true">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/03/10 20:44:15</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
         <v>16</v>
       </c>
@@ -818,26 +862,26 @@
       <c r="C11" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D11" s="4">
+      <c r="D11" s="4" t="n">
         <v>5</v>
       </c>
       <c r="E11" s="5"/>
       <c r="F11" s="6" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>2026/03/10 17:33:27</v>
-      </c>
-      <c r="G11" s="4">
+        <f aca="true">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/03/10 20:44:15</v>
+      </c>
+      <c r="G11" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H11" s="6" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>2026/03/10 17:33:27</v>
-      </c>
-      <c r="I11" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
+        <f aca="true">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/03/10 20:44:15</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
         <v>16</v>
       </c>
@@ -847,26 +891,26 @@
       <c r="C12" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="4">
+      <c r="D12" s="4" t="n">
         <v>6</v>
       </c>
       <c r="E12" s="5"/>
       <c r="F12" s="6" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>2026/03/10 17:33:27</v>
-      </c>
-      <c r="G12" s="4">
+        <f aca="true">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/03/10 20:44:15</v>
+      </c>
+      <c r="G12" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H12" s="6" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>2026/03/10 17:33:27</v>
-      </c>
-      <c r="I12" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
+        <f aca="true">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/03/10 20:44:15</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
         <v>28</v>
       </c>
@@ -876,26 +920,26 @@
       <c r="C13" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="4">
+      <c r="D13" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E13" s="5"/>
       <c r="F13" s="6" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>2026/03/10 17:33:27</v>
-      </c>
-      <c r="G13" s="4">
+        <f aca="true">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/03/10 20:44:15</v>
+      </c>
+      <c r="G13" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H13" s="6" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>2026/03/10 17:33:27</v>
-      </c>
-      <c r="I13" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
+        <f aca="true">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/03/10 20:44:15</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
         <v>28</v>
       </c>
@@ -905,26 +949,26 @@
       <c r="C14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="4">
+      <c r="D14" s="4" t="n">
         <v>2</v>
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="6" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>2026/03/10 17:33:27</v>
-      </c>
-      <c r="G14" s="4">
+        <f aca="true">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/03/10 20:44:15</v>
+      </c>
+      <c r="G14" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H14" s="6" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>2026/03/10 17:33:27</v>
-      </c>
-      <c r="I14" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
+        <f aca="true">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/03/10 20:44:15</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
         <v>28</v>
       </c>
@@ -934,26 +978,26 @@
       <c r="C15" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="4">
+      <c r="D15" s="4" t="n">
         <v>3</v>
       </c>
       <c r="E15" s="5"/>
       <c r="F15" s="6" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>2026/03/10 17:33:27</v>
-      </c>
-      <c r="G15" s="4">
+        <f aca="true">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/03/10 20:44:15</v>
+      </c>
+      <c r="G15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H15" s="6" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>2026/03/10 17:33:27</v>
-      </c>
-      <c r="I15" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
+        <f aca="true">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/03/10 20:44:15</v>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
         <v>29</v>
       </c>
@@ -963,26 +1007,26 @@
       <c r="C16" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D16" s="4">
+      <c r="D16" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E16" s="5"/>
       <c r="F16" s="6" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>2026/03/10 17:33:27</v>
-      </c>
-      <c r="G16" s="4">
+        <f aca="true">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/03/10 20:44:15</v>
+      </c>
+      <c r="G16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H16" s="6" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>2026/03/10 17:33:27</v>
-      </c>
-      <c r="I16" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
+        <f aca="true">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/03/10 20:44:15</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
         <v>29</v>
       </c>
@@ -992,26 +1036,26 @@
       <c r="C17" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D17" s="4">
+      <c r="D17" s="4" t="n">
         <v>2</v>
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="6" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>2026/03/10 17:33:27</v>
-      </c>
-      <c r="G17" s="4">
+        <f aca="true">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/03/10 20:44:15</v>
+      </c>
+      <c r="G17" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H17" s="6" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>2026/03/10 17:33:27</v>
-      </c>
-      <c r="I17" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
+        <f aca="true">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/03/10 20:44:15</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
         <v>29</v>
       </c>
@@ -1021,26 +1065,26 @@
       <c r="C18" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D18" s="4">
+      <c r="D18" s="4" t="n">
         <v>3</v>
       </c>
       <c r="E18" s="5"/>
       <c r="F18" s="6" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>2026/03/10 17:33:27</v>
-      </c>
-      <c r="G18" s="4">
+        <f aca="true">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/03/10 20:44:15</v>
+      </c>
+      <c r="G18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H18" s="6" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>2026/03/10 17:33:27</v>
-      </c>
-      <c r="I18" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
+        <f aca="true">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/03/10 20:44:15</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
         <v>30</v>
       </c>
@@ -1053,21 +1097,21 @@
       <c r="D19" s="5"/>
       <c r="E19" s="5"/>
       <c r="F19" s="6" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>2026/03/10 17:33:27</v>
-      </c>
-      <c r="G19" s="4">
+        <f aca="true">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/03/10 20:44:15</v>
+      </c>
+      <c r="G19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H19" s="6" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>2026/03/10 17:33:27</v>
-      </c>
-      <c r="I19" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
+        <f aca="true">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/03/10 20:44:15</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
         <v>30</v>
       </c>
@@ -1080,21 +1124,21 @@
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
       <c r="F20" s="6" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>2026/03/10 17:33:27</v>
-      </c>
-      <c r="G20" s="4">
+        <f aca="true">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/03/10 20:44:15</v>
+      </c>
+      <c r="G20" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H20" s="6" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>2026/03/10 17:33:27</v>
-      </c>
-      <c r="I20" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
+        <f aca="true">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/03/10 20:44:15</v>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
         <v>30</v>
       </c>
@@ -1107,21 +1151,21 @@
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
       <c r="F21" s="6" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>2026/03/10 17:33:27</v>
-      </c>
-      <c r="G21" s="4">
+        <f aca="true">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/03/10 20:44:15</v>
+      </c>
+      <c r="G21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H21" s="6" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>2026/03/10 17:33:27</v>
-      </c>
-      <c r="I21" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
+        <f aca="true">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/03/10 20:44:15</v>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
         <v>35</v>
       </c>
@@ -1134,21 +1178,21 @@
       <c r="D22" s="5"/>
       <c r="E22" s="5"/>
       <c r="F22" s="6" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>2026/03/10 17:33:27</v>
-      </c>
-      <c r="G22" s="4">
+        <f aca="true">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/03/10 20:44:15</v>
+      </c>
+      <c r="G22" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H22" s="6" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>2026/03/10 17:33:27</v>
-      </c>
-      <c r="I22" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
+        <f aca="true">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/03/10 20:44:15</v>
+      </c>
+      <c r="I22" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
         <v>35</v>
       </c>
@@ -1161,21 +1205,21 @@
       <c r="D23" s="5"/>
       <c r="E23" s="5"/>
       <c r="F23" s="6" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>2026/03/10 17:33:27</v>
-      </c>
-      <c r="G23" s="4">
+        <f aca="true">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/03/10 20:44:15</v>
+      </c>
+      <c r="G23" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H23" s="6" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>2026/03/10 17:33:27</v>
-      </c>
-      <c r="I23" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
+        <f aca="true">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/03/10 20:44:15</v>
+      </c>
+      <c r="I23" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
         <v>35</v>
       </c>
@@ -1188,35 +1232,30 @@
       <c r="D24" s="5"/>
       <c r="E24" s="5"/>
       <c r="F24" s="6" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>2026/03/10 17:33:27</v>
-      </c>
-      <c r="G24" s="4">
+        <f aca="true">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/03/10 20:44:15</v>
+      </c>
+      <c r="G24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H24" s="6" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>2026/03/10 17:33:27</v>
-      </c>
-      <c r="I24" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1048570" ht="13.2" x14ac:dyDescent="0.45"/>
-    <row r="1048571" ht="13.2" x14ac:dyDescent="0.45"/>
-    <row r="1048572" ht="13.2" x14ac:dyDescent="0.45"/>
-    <row r="1048573" ht="13.2" x14ac:dyDescent="0.45"/>
-    <row r="1048574" ht="13.2" x14ac:dyDescent="0.45"/>
-    <row r="1048575" ht="13.2" x14ac:dyDescent="0.45"/>
-    <row r="1048576" ht="13.2" x14ac:dyDescent="0.45"/>
+        <f aca="true">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/03/10 20:44:15</v>
+      </c>
+      <c r="I24" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1048576" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <autoFilter ref="A2:I24" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <phoneticPr fontId="4"/>
+  <autoFilter ref="A2:I24"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;R&amp;D &amp;T</oddHeader>
     <oddFooter>&amp;C&amp;P / &amp;N</oddFooter>
   </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/.schema/MSY_KBN_VAL.xlsx
+++ b/.schema/MSY_KBN_VAL.xlsx
@@ -1,21 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KTC0966\git\sample\.schema\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A5892F3-5BD3-419F-98CC-9E073315C0C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="EMARF.MSY_KBN_VAL" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="EMARF.MSY_KBN_VAL" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Titles" vbProcedure="false">'EMARF.MSY_KBN_VAL'!$2:$2</definedName>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'EMARF.MSY_KBN_VAL'!$A$2:$I$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">EMARF.MSY_KBN_VAL!$A$2:$I$24</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">EMARF.MSY_KBN_VAL!$2:$2</definedName>
   </definedNames>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -24,158 +38,144 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="39">
-  <si>
-    <t xml:space="preserve">KBN_NM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KBN_VAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KBN_VAL_MEI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HYOJI_ON</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CRITERIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INSERT_TS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INSERT_USER_ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UPDATE_TS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UPDATE_USER_ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHECK_F</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">なし</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">あり</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DELETE_F</t>
-  </si>
-  <si>
-    <t xml:space="preserve">削除</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PULLDOWN_KB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">１</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">２</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">３</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">４</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">５</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">６</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PULLDOWN_SB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RADIO_KB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STATUS_KB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">否認</t>
-  </si>
-  <si>
-    <t xml:space="preserve">登録</t>
-  </si>
-  <si>
-    <t xml:space="preserve">承認</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TSUKA_KB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">円</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ドル</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ユーロ</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="41">
+  <si>
+    <t>KBN_NM</t>
+  </si>
+  <si>
+    <t>KBN_VAL</t>
+  </si>
+  <si>
+    <t>KBN_VAL_MEI</t>
+  </si>
+  <si>
+    <t>HYOJI_ON</t>
+  </si>
+  <si>
+    <t>CRITERIA</t>
+  </si>
+  <si>
+    <t>INSERT_TS</t>
+  </si>
+  <si>
+    <t>INSERT_USER_ID</t>
+  </si>
+  <si>
+    <t>UPDATE_TS</t>
+  </si>
+  <si>
+    <t>UPDATE_USER_ID</t>
+  </si>
+  <si>
+    <t>CHECK_F</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>なし</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>あり</t>
+  </si>
+  <si>
+    <t>DELETE_F</t>
+  </si>
+  <si>
+    <t>削除</t>
+  </si>
+  <si>
+    <t>PULLDOWN_KB</t>
+  </si>
+  <si>
+    <t>１</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>２</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>３</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>４</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>５</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>６</t>
+  </si>
+  <si>
+    <t>PULLDOWN_SB</t>
+  </si>
+  <si>
+    <t>RADIO_KB</t>
+  </si>
+  <si>
+    <t>STATUS_KB</t>
+  </si>
+  <si>
+    <t>-1</t>
+  </si>
+  <si>
+    <t>否認</t>
+  </si>
+  <si>
+    <t>登録</t>
+  </si>
+  <si>
+    <t>承認</t>
+  </si>
+  <si>
+    <t>TSUKA_KB</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>JPY</t>
+  </si>
+  <si>
+    <t>EUR</t>
+  </si>
+  <si>
+    <t>GBP</t>
+  </si>
+  <si>
+    <t>CNY</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="0"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd\ h:mm:ss.000"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="176" formatCode="yyyy/mm/dd\ h:mm:ss.000"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="游ゴシック"/>
       <family val="2"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
@@ -186,7 +186,7 @@
       <charset val="128"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -198,6 +198,12 @@
       <color rgb="FFC0C0C0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
       <charset val="128"/>
     </font>
   </fonts>
@@ -216,121 +222,66 @@
     </fill>
   </fills>
   <borders count="2">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="21">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+  <cellStyleXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="7">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="7">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
-    <cellStyle name="標準 2" xfId="20"/>
+  <cellStyles count="2">
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="標準 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
   </cellStyles>
-  <dxfs count="4">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF87E7AD"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF000000"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC0C0C0"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -389,64 +340,76 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546a"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="e7e6e6"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472c4"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ed7d31"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a5a5a5"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="ffc000"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5b9bd5"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70ad47"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563c1"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954f72"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -478,7 +441,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -502,7 +465,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -562,36 +525,35 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:I1048576"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:I26"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12.1"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="13.4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="12.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="22.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="19.9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="22.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="20.7"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="10" style="1" width="8.8"/>
+    <col min="1" max="1" width="14.59765625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.09765625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="16.5" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.3984375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="12.5" style="1" customWidth="1"/>
+    <col min="6" max="6" width="22.5" style="1" customWidth="1"/>
+    <col min="7" max="7" width="19.8984375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="22.5" style="1" customWidth="1"/>
+    <col min="9" max="9" width="20.69921875" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:9" ht="13.2" x14ac:dyDescent="0.45"/>
+    <row r="2" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -620,7 +582,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
       <c r="A3" s="3" t="s">
         <v>9</v>
       </c>
@@ -630,26 +592,26 @@
       <c r="C3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="4" t="n">
+      <c r="D3" s="4">
         <v>1</v>
       </c>
       <c r="E3" s="5"/>
       <c r="F3" s="6" t="str">
-        <f aca="true">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
-        <v>2026/03/10 20:44:15</v>
-      </c>
-      <c r="G3" s="4" t="n">
+        <f t="shared" ref="F3:F26" ca="1" si="0">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/03/20 10:07:43</v>
+      </c>
+      <c r="G3" s="4">
         <v>0</v>
       </c>
       <c r="H3" s="6" t="str">
-        <f aca="true">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
-        <v>2026/03/10 20:44:15</v>
-      </c>
-      <c r="I3" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <f t="shared" ref="H3:H26" ca="1" si="1">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/03/20 10:07:43</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
       <c r="A4" s="3" t="s">
         <v>9</v>
       </c>
@@ -659,26 +621,26 @@
       <c r="C4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D4" s="4">
         <v>2</v>
       </c>
       <c r="E4" s="5"/>
       <c r="F4" s="6" t="str">
-        <f aca="true">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
-        <v>2026/03/10 20:44:15</v>
-      </c>
-      <c r="G4" s="4" t="n">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/03/20 10:07:43</v>
+      </c>
+      <c r="G4" s="4">
         <v>0</v>
       </c>
       <c r="H4" s="6" t="str">
-        <f aca="true">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
-        <v>2026/03/10 20:44:15</v>
-      </c>
-      <c r="I4" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <f t="shared" ca="1" si="1"/>
+        <v>2026/03/20 10:07:43</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
       <c r="A5" s="3" t="s">
         <v>14</v>
       </c>
@@ -688,26 +650,26 @@
       <c r="C5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" s="4">
         <v>1</v>
       </c>
       <c r="E5" s="5"/>
       <c r="F5" s="6" t="str">
-        <f aca="true">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
-        <v>2026/03/10 20:44:15</v>
-      </c>
-      <c r="G5" s="4" t="n">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/03/20 10:07:43</v>
+      </c>
+      <c r="G5" s="4">
         <v>0</v>
       </c>
       <c r="H5" s="6" t="str">
-        <f aca="true">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
-        <v>2026/03/10 20:44:15</v>
-      </c>
-      <c r="I5" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <f t="shared" ca="1" si="1"/>
+        <v>2026/03/20 10:07:43</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
       <c r="A6" s="3" t="s">
         <v>14</v>
       </c>
@@ -717,26 +679,26 @@
       <c r="C6" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D6" s="4">
         <v>2</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="6" t="str">
-        <f aca="true">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
-        <v>2026/03/10 20:44:15</v>
-      </c>
-      <c r="G6" s="4" t="n">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/03/20 10:07:43</v>
+      </c>
+      <c r="G6" s="4">
         <v>0</v>
       </c>
       <c r="H6" s="6" t="str">
-        <f aca="true">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
-        <v>2026/03/10 20:44:15</v>
-      </c>
-      <c r="I6" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <f t="shared" ca="1" si="1"/>
+        <v>2026/03/20 10:07:43</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
       <c r="A7" s="3" t="s">
         <v>16</v>
       </c>
@@ -746,26 +708,26 @@
       <c r="C7" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D7" s="4">
         <v>1</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="6" t="str">
-        <f aca="true">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
-        <v>2026/03/10 20:44:15</v>
-      </c>
-      <c r="G7" s="4" t="n">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/03/20 10:07:43</v>
+      </c>
+      <c r="G7" s="4">
         <v>0</v>
       </c>
       <c r="H7" s="6" t="str">
-        <f aca="true">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
-        <v>2026/03/10 20:44:15</v>
-      </c>
-      <c r="I7" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <f t="shared" ca="1" si="1"/>
+        <v>2026/03/20 10:07:43</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
       <c r="A8" s="3" t="s">
         <v>16</v>
       </c>
@@ -775,26 +737,26 @@
       <c r="C8" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="D8" s="4">
         <v>2</v>
       </c>
       <c r="E8" s="5"/>
       <c r="F8" s="6" t="str">
-        <f aca="true">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
-        <v>2026/03/10 20:44:15</v>
-      </c>
-      <c r="G8" s="4" t="n">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/03/20 10:07:43</v>
+      </c>
+      <c r="G8" s="4">
         <v>0</v>
       </c>
       <c r="H8" s="6" t="str">
-        <f aca="true">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
-        <v>2026/03/10 20:44:15</v>
-      </c>
-      <c r="I8" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <f t="shared" ca="1" si="1"/>
+        <v>2026/03/20 10:07:43</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
       <c r="A9" s="3" t="s">
         <v>16</v>
       </c>
@@ -804,26 +766,26 @@
       <c r="C9" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="D9" s="4">
         <v>3</v>
       </c>
       <c r="E9" s="5"/>
       <c r="F9" s="6" t="str">
-        <f aca="true">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
-        <v>2026/03/10 20:44:15</v>
-      </c>
-      <c r="G9" s="4" t="n">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/03/20 10:07:43</v>
+      </c>
+      <c r="G9" s="4">
         <v>0</v>
       </c>
       <c r="H9" s="6" t="str">
-        <f aca="true">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
-        <v>2026/03/10 20:44:15</v>
-      </c>
-      <c r="I9" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <f t="shared" ca="1" si="1"/>
+        <v>2026/03/20 10:07:43</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
       <c r="A10" s="3" t="s">
         <v>16</v>
       </c>
@@ -833,26 +795,26 @@
       <c r="C10" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="4" t="n">
+      <c r="D10" s="4">
         <v>4</v>
       </c>
       <c r="E10" s="5"/>
       <c r="F10" s="6" t="str">
-        <f aca="true">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
-        <v>2026/03/10 20:44:15</v>
-      </c>
-      <c r="G10" s="4" t="n">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/03/20 10:07:43</v>
+      </c>
+      <c r="G10" s="4">
         <v>0</v>
       </c>
       <c r="H10" s="6" t="str">
-        <f aca="true">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
-        <v>2026/03/10 20:44:15</v>
-      </c>
-      <c r="I10" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <f t="shared" ca="1" si="1"/>
+        <v>2026/03/20 10:07:43</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
       <c r="A11" s="3" t="s">
         <v>16</v>
       </c>
@@ -862,26 +824,26 @@
       <c r="C11" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D11" s="4" t="n">
+      <c r="D11" s="4">
         <v>5</v>
       </c>
       <c r="E11" s="5"/>
       <c r="F11" s="6" t="str">
-        <f aca="true">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
-        <v>2026/03/10 20:44:15</v>
-      </c>
-      <c r="G11" s="4" t="n">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/03/20 10:07:43</v>
+      </c>
+      <c r="G11" s="4">
         <v>0</v>
       </c>
       <c r="H11" s="6" t="str">
-        <f aca="true">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
-        <v>2026/03/10 20:44:15</v>
-      </c>
-      <c r="I11" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <f t="shared" ca="1" si="1"/>
+        <v>2026/03/20 10:07:43</v>
+      </c>
+      <c r="I11" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
       <c r="A12" s="3" t="s">
         <v>16</v>
       </c>
@@ -891,26 +853,26 @@
       <c r="C12" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="4" t="n">
+      <c r="D12" s="4">
         <v>6</v>
       </c>
       <c r="E12" s="5"/>
       <c r="F12" s="6" t="str">
-        <f aca="true">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
-        <v>2026/03/10 20:44:15</v>
-      </c>
-      <c r="G12" s="4" t="n">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/03/20 10:07:43</v>
+      </c>
+      <c r="G12" s="4">
         <v>0</v>
       </c>
       <c r="H12" s="6" t="str">
-        <f aca="true">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
-        <v>2026/03/10 20:44:15</v>
-      </c>
-      <c r="I12" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <f t="shared" ca="1" si="1"/>
+        <v>2026/03/20 10:07:43</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
       <c r="A13" s="3" t="s">
         <v>28</v>
       </c>
@@ -920,26 +882,26 @@
       <c r="C13" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="4" t="n">
+      <c r="D13" s="4">
         <v>1</v>
       </c>
       <c r="E13" s="5"/>
       <c r="F13" s="6" t="str">
-        <f aca="true">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
-        <v>2026/03/10 20:44:15</v>
-      </c>
-      <c r="G13" s="4" t="n">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/03/20 10:07:43</v>
+      </c>
+      <c r="G13" s="4">
         <v>0</v>
       </c>
       <c r="H13" s="6" t="str">
-        <f aca="true">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
-        <v>2026/03/10 20:44:15</v>
-      </c>
-      <c r="I13" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <f t="shared" ca="1" si="1"/>
+        <v>2026/03/20 10:07:43</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
       <c r="A14" s="3" t="s">
         <v>28</v>
       </c>
@@ -949,26 +911,26 @@
       <c r="C14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="4" t="n">
+      <c r="D14" s="4">
         <v>2</v>
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="6" t="str">
-        <f aca="true">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
-        <v>2026/03/10 20:44:15</v>
-      </c>
-      <c r="G14" s="4" t="n">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/03/20 10:07:43</v>
+      </c>
+      <c r="G14" s="4">
         <v>0</v>
       </c>
       <c r="H14" s="6" t="str">
-        <f aca="true">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
-        <v>2026/03/10 20:44:15</v>
-      </c>
-      <c r="I14" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <f t="shared" ca="1" si="1"/>
+        <v>2026/03/20 10:07:43</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
       <c r="A15" s="3" t="s">
         <v>28</v>
       </c>
@@ -978,26 +940,26 @@
       <c r="C15" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="4" t="n">
+      <c r="D15" s="4">
         <v>3</v>
       </c>
       <c r="E15" s="5"/>
       <c r="F15" s="6" t="str">
-        <f aca="true">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
-        <v>2026/03/10 20:44:15</v>
-      </c>
-      <c r="G15" s="4" t="n">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/03/20 10:07:43</v>
+      </c>
+      <c r="G15" s="4">
         <v>0</v>
       </c>
       <c r="H15" s="6" t="str">
-        <f aca="true">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
-        <v>2026/03/10 20:44:15</v>
-      </c>
-      <c r="I15" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <f t="shared" ca="1" si="1"/>
+        <v>2026/03/20 10:07:43</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
       <c r="A16" s="3" t="s">
         <v>29</v>
       </c>
@@ -1007,26 +969,26 @@
       <c r="C16" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D16" s="4" t="n">
+      <c r="D16" s="4">
         <v>1</v>
       </c>
       <c r="E16" s="5"/>
       <c r="F16" s="6" t="str">
-        <f aca="true">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
-        <v>2026/03/10 20:44:15</v>
-      </c>
-      <c r="G16" s="4" t="n">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/03/20 10:07:43</v>
+      </c>
+      <c r="G16" s="4">
         <v>0</v>
       </c>
       <c r="H16" s="6" t="str">
-        <f aca="true">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
-        <v>2026/03/10 20:44:15</v>
-      </c>
-      <c r="I16" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <f t="shared" ca="1" si="1"/>
+        <v>2026/03/20 10:07:43</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
       <c r="A17" s="3" t="s">
         <v>29</v>
       </c>
@@ -1036,26 +998,26 @@
       <c r="C17" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D17" s="4" t="n">
+      <c r="D17" s="4">
         <v>2</v>
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="6" t="str">
-        <f aca="true">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
-        <v>2026/03/10 20:44:15</v>
-      </c>
-      <c r="G17" s="4" t="n">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/03/20 10:07:43</v>
+      </c>
+      <c r="G17" s="4">
         <v>0</v>
       </c>
       <c r="H17" s="6" t="str">
-        <f aca="true">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
-        <v>2026/03/10 20:44:15</v>
-      </c>
-      <c r="I17" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <f t="shared" ca="1" si="1"/>
+        <v>2026/03/20 10:07:43</v>
+      </c>
+      <c r="I17" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
       <c r="A18" s="3" t="s">
         <v>29</v>
       </c>
@@ -1065,26 +1027,26 @@
       <c r="C18" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D18" s="4" t="n">
+      <c r="D18" s="4">
         <v>3</v>
       </c>
       <c r="E18" s="5"/>
       <c r="F18" s="6" t="str">
-        <f aca="true">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
-        <v>2026/03/10 20:44:15</v>
-      </c>
-      <c r="G18" s="4" t="n">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/03/20 10:07:43</v>
+      </c>
+      <c r="G18" s="4">
         <v>0</v>
       </c>
       <c r="H18" s="6" t="str">
-        <f aca="true">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
-        <v>2026/03/10 20:44:15</v>
-      </c>
-      <c r="I18" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <f t="shared" ca="1" si="1"/>
+        <v>2026/03/20 10:07:43</v>
+      </c>
+      <c r="I18" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
       <c r="A19" s="3" t="s">
         <v>30</v>
       </c>
@@ -1097,21 +1059,21 @@
       <c r="D19" s="5"/>
       <c r="E19" s="5"/>
       <c r="F19" s="6" t="str">
-        <f aca="true">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
-        <v>2026/03/10 20:44:15</v>
-      </c>
-      <c r="G19" s="4" t="n">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/03/20 10:07:43</v>
+      </c>
+      <c r="G19" s="4">
         <v>0</v>
       </c>
       <c r="H19" s="6" t="str">
-        <f aca="true">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
-        <v>2026/03/10 20:44:15</v>
-      </c>
-      <c r="I19" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <f t="shared" ca="1" si="1"/>
+        <v>2026/03/20 10:07:43</v>
+      </c>
+      <c r="I19" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
       <c r="A20" s="3" t="s">
         <v>30</v>
       </c>
@@ -1124,21 +1086,21 @@
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
       <c r="F20" s="6" t="str">
-        <f aca="true">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
-        <v>2026/03/10 20:44:15</v>
-      </c>
-      <c r="G20" s="4" t="n">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/03/20 10:07:43</v>
+      </c>
+      <c r="G20" s="4">
         <v>0</v>
       </c>
       <c r="H20" s="6" t="str">
-        <f aca="true">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
-        <v>2026/03/10 20:44:15</v>
-      </c>
-      <c r="I20" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <f t="shared" ca="1" si="1"/>
+        <v>2026/03/20 10:07:43</v>
+      </c>
+      <c r="I20" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
       <c r="A21" s="3" t="s">
         <v>30</v>
       </c>
@@ -1151,21 +1113,21 @@
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
       <c r="F21" s="6" t="str">
-        <f aca="true">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
-        <v>2026/03/10 20:44:15</v>
-      </c>
-      <c r="G21" s="4" t="n">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/03/20 10:07:43</v>
+      </c>
+      <c r="G21" s="4">
         <v>0</v>
       </c>
       <c r="H21" s="6" t="str">
-        <f aca="true">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
-        <v>2026/03/10 20:44:15</v>
-      </c>
-      <c r="I21" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <f t="shared" ca="1" si="1"/>
+        <v>2026/03/20 10:07:43</v>
+      </c>
+      <c r="I21" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
       <c r="A22" s="3" t="s">
         <v>35</v>
       </c>
@@ -1173,26 +1135,26 @@
         <v>10</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D22" s="5"/>
       <c r="E22" s="5"/>
       <c r="F22" s="6" t="str">
-        <f aca="true">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
-        <v>2026/03/10 20:44:15</v>
-      </c>
-      <c r="G22" s="4" t="n">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/03/20 10:07:43</v>
+      </c>
+      <c r="G22" s="4">
         <v>0</v>
       </c>
       <c r="H22" s="6" t="str">
-        <f aca="true">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
-        <v>2026/03/10 20:44:15</v>
-      </c>
-      <c r="I22" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <f t="shared" ca="1" si="1"/>
+        <v>2026/03/20 10:07:43</v>
+      </c>
+      <c r="I22" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
       <c r="A23" s="3" t="s">
         <v>35</v>
       </c>
@@ -1200,26 +1162,26 @@
         <v>12</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D23" s="5"/>
       <c r="E23" s="5"/>
       <c r="F23" s="6" t="str">
-        <f aca="true">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
-        <v>2026/03/10 20:44:15</v>
-      </c>
-      <c r="G23" s="4" t="n">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/03/20 10:07:43</v>
+      </c>
+      <c r="G23" s="4">
         <v>0</v>
       </c>
       <c r="H23" s="6" t="str">
-        <f aca="true">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
-        <v>2026/03/10 20:44:15</v>
-      </c>
-      <c r="I23" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <f t="shared" ca="1" si="1"/>
+        <v>2026/03/20 10:07:43</v>
+      </c>
+      <c r="I23" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
       <c r="A24" s="3" t="s">
         <v>35</v>
       </c>
@@ -1232,30 +1194,82 @@
       <c r="D24" s="5"/>
       <c r="E24" s="5"/>
       <c r="F24" s="6" t="str">
-        <f aca="true">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
-        <v>2026/03/10 20:44:15</v>
-      </c>
-      <c r="G24" s="4" t="n">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/03/20 10:07:43</v>
+      </c>
+      <c r="G24" s="4">
         <v>0</v>
       </c>
       <c r="H24" s="6" t="str">
-        <f aca="true">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
-        <v>2026/03/10 20:44:15</v>
-      </c>
-      <c r="I24" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1048576" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+        <f t="shared" ca="1" si="1"/>
+        <v>2026/03/20 10:07:43</v>
+      </c>
+      <c r="I24" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
+      <c r="A25" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="6" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/03/20 10:07:43</v>
+      </c>
+      <c r="G25" s="4">
+        <v>0</v>
+      </c>
+      <c r="H25" s="6" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>2026/03/20 10:07:43</v>
+      </c>
+      <c r="I25" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
+      <c r="A26" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="6" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/03/20 10:07:43</v>
+      </c>
+      <c r="G26" s="4">
+        <v>0</v>
+      </c>
+      <c r="H26" s="6" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>2026/03/20 10:07:43</v>
+      </c>
+      <c r="I26" s="4">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I24"/>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <autoFilter ref="A2:I24" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <phoneticPr fontId="4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter>
     <oddHeader>&amp;R&amp;D &amp;T</oddHeader>
     <oddFooter>&amp;C&amp;P / &amp;N</oddFooter>
   </headerFooter>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/.schema/MSY_KBN_VAL.xlsx
+++ b/.schema/MSY_KBN_VAL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KTC0966\git\sample\.schema\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A5892F3-5BD3-419F-98CC-9E073315C0C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF061E44-30D7-4157-9F65-694462523C06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -139,9 +139,6 @@
     <t>否認</t>
   </si>
   <si>
-    <t>登録</t>
-  </si>
-  <si>
     <t>承認</t>
   </si>
   <si>
@@ -161,6 +158,13 @@
   </si>
   <si>
     <t>CNY</t>
+  </si>
+  <si>
+    <t>申請</t>
+    <rPh sb="0" eb="2">
+      <t>シンセイ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
   </si>
 </sst>
 </file>
@@ -598,14 +602,14 @@
       <c r="E3" s="5"/>
       <c r="F3" s="6" t="str">
         <f t="shared" ref="F3:F26" ca="1" si="0">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
-        <v>2026/03/20 10:07:43</v>
+        <v>2026/03/24 08:17:34</v>
       </c>
       <c r="G3" s="4">
         <v>0</v>
       </c>
       <c r="H3" s="6" t="str">
         <f t="shared" ref="H3:H26" ca="1" si="1">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
-        <v>2026/03/20 10:07:43</v>
+        <v>2026/03/24 08:17:34</v>
       </c>
       <c r="I3" s="4">
         <v>0</v>
@@ -627,14 +631,14 @@
       <c r="E4" s="5"/>
       <c r="F4" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/03/20 10:07:43</v>
+        <v>2026/03/24 08:17:34</v>
       </c>
       <c r="G4" s="4">
         <v>0</v>
       </c>
       <c r="H4" s="6" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/03/20 10:07:43</v>
+        <v>2026/03/24 08:17:34</v>
       </c>
       <c r="I4" s="4">
         <v>0</v>
@@ -656,14 +660,14 @@
       <c r="E5" s="5"/>
       <c r="F5" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/03/20 10:07:43</v>
+        <v>2026/03/24 08:17:34</v>
       </c>
       <c r="G5" s="4">
         <v>0</v>
       </c>
       <c r="H5" s="6" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/03/20 10:07:43</v>
+        <v>2026/03/24 08:17:34</v>
       </c>
       <c r="I5" s="4">
         <v>0</v>
@@ -685,14 +689,14 @@
       <c r="E6" s="5"/>
       <c r="F6" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/03/20 10:07:43</v>
+        <v>2026/03/24 08:17:34</v>
       </c>
       <c r="G6" s="4">
         <v>0</v>
       </c>
       <c r="H6" s="6" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/03/20 10:07:43</v>
+        <v>2026/03/24 08:17:34</v>
       </c>
       <c r="I6" s="4">
         <v>0</v>
@@ -714,14 +718,14 @@
       <c r="E7" s="5"/>
       <c r="F7" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/03/20 10:07:43</v>
+        <v>2026/03/24 08:17:34</v>
       </c>
       <c r="G7" s="4">
         <v>0</v>
       </c>
       <c r="H7" s="6" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/03/20 10:07:43</v>
+        <v>2026/03/24 08:17:34</v>
       </c>
       <c r="I7" s="4">
         <v>0</v>
@@ -743,14 +747,14 @@
       <c r="E8" s="5"/>
       <c r="F8" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/03/20 10:07:43</v>
+        <v>2026/03/24 08:17:34</v>
       </c>
       <c r="G8" s="4">
         <v>0</v>
       </c>
       <c r="H8" s="6" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/03/20 10:07:43</v>
+        <v>2026/03/24 08:17:34</v>
       </c>
       <c r="I8" s="4">
         <v>0</v>
@@ -772,14 +776,14 @@
       <c r="E9" s="5"/>
       <c r="F9" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/03/20 10:07:43</v>
+        <v>2026/03/24 08:17:34</v>
       </c>
       <c r="G9" s="4">
         <v>0</v>
       </c>
       <c r="H9" s="6" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/03/20 10:07:43</v>
+        <v>2026/03/24 08:17:34</v>
       </c>
       <c r="I9" s="4">
         <v>0</v>
@@ -801,14 +805,14 @@
       <c r="E10" s="5"/>
       <c r="F10" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/03/20 10:07:43</v>
+        <v>2026/03/24 08:17:34</v>
       </c>
       <c r="G10" s="4">
         <v>0</v>
       </c>
       <c r="H10" s="6" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/03/20 10:07:43</v>
+        <v>2026/03/24 08:17:34</v>
       </c>
       <c r="I10" s="4">
         <v>0</v>
@@ -830,14 +834,14 @@
       <c r="E11" s="5"/>
       <c r="F11" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/03/20 10:07:43</v>
+        <v>2026/03/24 08:17:34</v>
       </c>
       <c r="G11" s="4">
         <v>0</v>
       </c>
       <c r="H11" s="6" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/03/20 10:07:43</v>
+        <v>2026/03/24 08:17:34</v>
       </c>
       <c r="I11" s="4">
         <v>0</v>
@@ -859,14 +863,14 @@
       <c r="E12" s="5"/>
       <c r="F12" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/03/20 10:07:43</v>
+        <v>2026/03/24 08:17:34</v>
       </c>
       <c r="G12" s="4">
         <v>0</v>
       </c>
       <c r="H12" s="6" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/03/20 10:07:43</v>
+        <v>2026/03/24 08:17:34</v>
       </c>
       <c r="I12" s="4">
         <v>0</v>
@@ -888,14 +892,14 @@
       <c r="E13" s="5"/>
       <c r="F13" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/03/20 10:07:43</v>
+        <v>2026/03/24 08:17:34</v>
       </c>
       <c r="G13" s="4">
         <v>0</v>
       </c>
       <c r="H13" s="6" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/03/20 10:07:43</v>
+        <v>2026/03/24 08:17:34</v>
       </c>
       <c r="I13" s="4">
         <v>0</v>
@@ -917,14 +921,14 @@
       <c r="E14" s="5"/>
       <c r="F14" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/03/20 10:07:43</v>
+        <v>2026/03/24 08:17:34</v>
       </c>
       <c r="G14" s="4">
         <v>0</v>
       </c>
       <c r="H14" s="6" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/03/20 10:07:43</v>
+        <v>2026/03/24 08:17:34</v>
       </c>
       <c r="I14" s="4">
         <v>0</v>
@@ -946,14 +950,14 @@
       <c r="E15" s="5"/>
       <c r="F15" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/03/20 10:07:43</v>
+        <v>2026/03/24 08:17:34</v>
       </c>
       <c r="G15" s="4">
         <v>0</v>
       </c>
       <c r="H15" s="6" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/03/20 10:07:43</v>
+        <v>2026/03/24 08:17:34</v>
       </c>
       <c r="I15" s="4">
         <v>0</v>
@@ -975,14 +979,14 @@
       <c r="E16" s="5"/>
       <c r="F16" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/03/20 10:07:43</v>
+        <v>2026/03/24 08:17:34</v>
       </c>
       <c r="G16" s="4">
         <v>0</v>
       </c>
       <c r="H16" s="6" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/03/20 10:07:43</v>
+        <v>2026/03/24 08:17:34</v>
       </c>
       <c r="I16" s="4">
         <v>0</v>
@@ -1004,14 +1008,14 @@
       <c r="E17" s="5"/>
       <c r="F17" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/03/20 10:07:43</v>
+        <v>2026/03/24 08:17:34</v>
       </c>
       <c r="G17" s="4">
         <v>0</v>
       </c>
       <c r="H17" s="6" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/03/20 10:07:43</v>
+        <v>2026/03/24 08:17:34</v>
       </c>
       <c r="I17" s="4">
         <v>0</v>
@@ -1033,14 +1037,14 @@
       <c r="E18" s="5"/>
       <c r="F18" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/03/20 10:07:43</v>
+        <v>2026/03/24 08:17:34</v>
       </c>
       <c r="G18" s="4">
         <v>0</v>
       </c>
       <c r="H18" s="6" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/03/20 10:07:43</v>
+        <v>2026/03/24 08:17:34</v>
       </c>
       <c r="I18" s="4">
         <v>0</v>
@@ -1060,14 +1064,14 @@
       <c r="E19" s="5"/>
       <c r="F19" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/03/20 10:07:43</v>
+        <v>2026/03/24 08:17:34</v>
       </c>
       <c r="G19" s="4">
         <v>0</v>
       </c>
       <c r="H19" s="6" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/03/20 10:07:43</v>
+        <v>2026/03/24 08:17:34</v>
       </c>
       <c r="I19" s="4">
         <v>0</v>
@@ -1081,20 +1085,20 @@
         <v>10</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
       <c r="F20" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/03/20 10:07:43</v>
+        <v>2026/03/24 08:17:34</v>
       </c>
       <c r="G20" s="4">
         <v>0</v>
       </c>
       <c r="H20" s="6" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/03/20 10:07:43</v>
+        <v>2026/03/24 08:17:34</v>
       </c>
       <c r="I20" s="4">
         <v>0</v>
@@ -1108,20 +1112,20 @@
         <v>12</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
       <c r="F21" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/03/20 10:07:43</v>
+        <v>2026/03/24 08:17:34</v>
       </c>
       <c r="G21" s="4">
         <v>0</v>
       </c>
       <c r="H21" s="6" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/03/20 10:07:43</v>
+        <v>2026/03/24 08:17:34</v>
       </c>
       <c r="I21" s="4">
         <v>0</v>
@@ -1129,26 +1133,26 @@
     </row>
     <row r="22" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
       <c r="A22" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D22" s="5"/>
       <c r="E22" s="5"/>
       <c r="F22" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/03/20 10:07:43</v>
+        <v>2026/03/24 08:17:34</v>
       </c>
       <c r="G22" s="4">
         <v>0</v>
       </c>
       <c r="H22" s="6" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/03/20 10:07:43</v>
+        <v>2026/03/24 08:17:34</v>
       </c>
       <c r="I22" s="4">
         <v>0</v>
@@ -1156,26 +1160,26 @@
     </row>
     <row r="23" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
       <c r="A23" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D23" s="5"/>
       <c r="E23" s="5"/>
       <c r="F23" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/03/20 10:07:43</v>
+        <v>2026/03/24 08:17:34</v>
       </c>
       <c r="G23" s="4">
         <v>0</v>
       </c>
       <c r="H23" s="6" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/03/20 10:07:43</v>
+        <v>2026/03/24 08:17:34</v>
       </c>
       <c r="I23" s="4">
         <v>0</v>
@@ -1183,26 +1187,26 @@
     </row>
     <row r="24" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
       <c r="A24" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D24" s="5"/>
       <c r="E24" s="5"/>
       <c r="F24" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/03/20 10:07:43</v>
+        <v>2026/03/24 08:17:34</v>
       </c>
       <c r="G24" s="4">
         <v>0</v>
       </c>
       <c r="H24" s="6" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/03/20 10:07:43</v>
+        <v>2026/03/24 08:17:34</v>
       </c>
       <c r="I24" s="4">
         <v>0</v>
@@ -1210,26 +1214,26 @@
     </row>
     <row r="25" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
       <c r="A25" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D25" s="5"/>
       <c r="E25" s="5"/>
       <c r="F25" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/03/20 10:07:43</v>
+        <v>2026/03/24 08:17:34</v>
       </c>
       <c r="G25" s="4">
         <v>0</v>
       </c>
       <c r="H25" s="6" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/03/20 10:07:43</v>
+        <v>2026/03/24 08:17:34</v>
       </c>
       <c r="I25" s="4">
         <v>0</v>
@@ -1237,26 +1241,26 @@
     </row>
     <row r="26" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
       <c r="A26" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
       <c r="F26" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/03/20 10:07:43</v>
+        <v>2026/03/24 08:17:34</v>
       </c>
       <c r="G26" s="4">
         <v>0</v>
       </c>
       <c r="H26" s="6" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/03/20 10:07:43</v>
+        <v>2026/03/24 08:17:34</v>
       </c>
       <c r="I26" s="4">
         <v>0</v>

--- a/.schema/MSY_KBN_VAL.xlsx
+++ b/.schema/MSY_KBN_VAL.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KTC0966\git\sample\.schema\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF061E44-30D7-4157-9F65-694462523C06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24F00C45-A58D-46D0-A12F-6C0EF344875A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="44">
   <si>
     <t>KBN_NM</t>
   </si>
@@ -163,6 +163,27 @@
     <t>申請</t>
     <rPh sb="0" eb="2">
       <t>シンセイ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>KADOBI_F</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>非稼働日</t>
+    <rPh sb="0" eb="1">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="1" eb="4">
+      <t>カドウビ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>稼働日</t>
+    <rPh sb="0" eb="3">
+      <t>カドウビ</t>
     </rPh>
     <phoneticPr fontId="4"/>
   </si>
@@ -541,7 +562,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14.59765625" style="1" customWidth="1"/>
@@ -601,15 +622,15 @@
       </c>
       <c r="E3" s="5"/>
       <c r="F3" s="6" t="str">
-        <f t="shared" ref="F3:F26" ca="1" si="0">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
-        <v>2026/03/24 08:17:34</v>
+        <f t="shared" ref="F3:F28" ca="1" si="0">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/07/22 15:36:02</v>
       </c>
       <c r="G3" s="4">
         <v>0</v>
       </c>
       <c r="H3" s="6" t="str">
-        <f t="shared" ref="H3:H26" ca="1" si="1">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
-        <v>2026/03/24 08:17:34</v>
+        <f t="shared" ref="H3:H28" ca="1" si="1">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/07/22 15:36:02</v>
       </c>
       <c r="I3" s="4">
         <v>0</v>
@@ -631,14 +652,14 @@
       <c r="E4" s="5"/>
       <c r="F4" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/03/24 08:17:34</v>
+        <v>2026/07/22 15:36:02</v>
       </c>
       <c r="G4" s="4">
         <v>0</v>
       </c>
       <c r="H4" s="6" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/03/24 08:17:34</v>
+        <v>2026/07/22 15:36:02</v>
       </c>
       <c r="I4" s="4">
         <v>0</v>
@@ -660,14 +681,14 @@
       <c r="E5" s="5"/>
       <c r="F5" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/03/24 08:17:34</v>
+        <v>2026/07/22 15:36:02</v>
       </c>
       <c r="G5" s="4">
         <v>0</v>
       </c>
       <c r="H5" s="6" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/03/24 08:17:34</v>
+        <v>2026/07/22 15:36:02</v>
       </c>
       <c r="I5" s="4">
         <v>0</v>
@@ -689,14 +710,14 @@
       <c r="E6" s="5"/>
       <c r="F6" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/03/24 08:17:34</v>
+        <v>2026/07/22 15:36:02</v>
       </c>
       <c r="G6" s="4">
         <v>0</v>
       </c>
       <c r="H6" s="6" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/03/24 08:17:34</v>
+        <v>2026/07/22 15:36:02</v>
       </c>
       <c r="I6" s="4">
         <v>0</v>
@@ -718,14 +739,14 @@
       <c r="E7" s="5"/>
       <c r="F7" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/03/24 08:17:34</v>
+        <v>2026/07/22 15:36:02</v>
       </c>
       <c r="G7" s="4">
         <v>0</v>
       </c>
       <c r="H7" s="6" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/03/24 08:17:34</v>
+        <v>2026/07/22 15:36:02</v>
       </c>
       <c r="I7" s="4">
         <v>0</v>
@@ -747,14 +768,14 @@
       <c r="E8" s="5"/>
       <c r="F8" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/03/24 08:17:34</v>
+        <v>2026/07/22 15:36:02</v>
       </c>
       <c r="G8" s="4">
         <v>0</v>
       </c>
       <c r="H8" s="6" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/03/24 08:17:34</v>
+        <v>2026/07/22 15:36:02</v>
       </c>
       <c r="I8" s="4">
         <v>0</v>
@@ -776,14 +797,14 @@
       <c r="E9" s="5"/>
       <c r="F9" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/03/24 08:17:34</v>
+        <v>2026/07/22 15:36:02</v>
       </c>
       <c r="G9" s="4">
         <v>0</v>
       </c>
       <c r="H9" s="6" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/03/24 08:17:34</v>
+        <v>2026/07/22 15:36:02</v>
       </c>
       <c r="I9" s="4">
         <v>0</v>
@@ -805,14 +826,14 @@
       <c r="E10" s="5"/>
       <c r="F10" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/03/24 08:17:34</v>
+        <v>2026/07/22 15:36:02</v>
       </c>
       <c r="G10" s="4">
         <v>0</v>
       </c>
       <c r="H10" s="6" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/03/24 08:17:34</v>
+        <v>2026/07/22 15:36:02</v>
       </c>
       <c r="I10" s="4">
         <v>0</v>
@@ -834,14 +855,14 @@
       <c r="E11" s="5"/>
       <c r="F11" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/03/24 08:17:34</v>
+        <v>2026/07/22 15:36:02</v>
       </c>
       <c r="G11" s="4">
         <v>0</v>
       </c>
       <c r="H11" s="6" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/03/24 08:17:34</v>
+        <v>2026/07/22 15:36:02</v>
       </c>
       <c r="I11" s="4">
         <v>0</v>
@@ -863,14 +884,14 @@
       <c r="E12" s="5"/>
       <c r="F12" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/03/24 08:17:34</v>
+        <v>2026/07/22 15:36:02</v>
       </c>
       <c r="G12" s="4">
         <v>0</v>
       </c>
       <c r="H12" s="6" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/03/24 08:17:34</v>
+        <v>2026/07/22 15:36:02</v>
       </c>
       <c r="I12" s="4">
         <v>0</v>
@@ -892,14 +913,14 @@
       <c r="E13" s="5"/>
       <c r="F13" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/03/24 08:17:34</v>
+        <v>2026/07/22 15:36:02</v>
       </c>
       <c r="G13" s="4">
         <v>0</v>
       </c>
       <c r="H13" s="6" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/03/24 08:17:34</v>
+        <v>2026/07/22 15:36:02</v>
       </c>
       <c r="I13" s="4">
         <v>0</v>
@@ -921,14 +942,14 @@
       <c r="E14" s="5"/>
       <c r="F14" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/03/24 08:17:34</v>
+        <v>2026/07/22 15:36:02</v>
       </c>
       <c r="G14" s="4">
         <v>0</v>
       </c>
       <c r="H14" s="6" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/03/24 08:17:34</v>
+        <v>2026/07/22 15:36:02</v>
       </c>
       <c r="I14" s="4">
         <v>0</v>
@@ -950,14 +971,14 @@
       <c r="E15" s="5"/>
       <c r="F15" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/03/24 08:17:34</v>
+        <v>2026/07/22 15:36:02</v>
       </c>
       <c r="G15" s="4">
         <v>0</v>
       </c>
       <c r="H15" s="6" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/03/24 08:17:34</v>
+        <v>2026/07/22 15:36:02</v>
       </c>
       <c r="I15" s="4">
         <v>0</v>
@@ -979,14 +1000,14 @@
       <c r="E16" s="5"/>
       <c r="F16" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/03/24 08:17:34</v>
+        <v>2026/07/22 15:36:02</v>
       </c>
       <c r="G16" s="4">
         <v>0</v>
       </c>
       <c r="H16" s="6" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/03/24 08:17:34</v>
+        <v>2026/07/22 15:36:02</v>
       </c>
       <c r="I16" s="4">
         <v>0</v>
@@ -1008,14 +1029,14 @@
       <c r="E17" s="5"/>
       <c r="F17" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/03/24 08:17:34</v>
+        <v>2026/07/22 15:36:02</v>
       </c>
       <c r="G17" s="4">
         <v>0</v>
       </c>
       <c r="H17" s="6" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/03/24 08:17:34</v>
+        <v>2026/07/22 15:36:02</v>
       </c>
       <c r="I17" s="4">
         <v>0</v>
@@ -1037,14 +1058,14 @@
       <c r="E18" s="5"/>
       <c r="F18" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/03/24 08:17:34</v>
+        <v>2026/07/22 15:36:02</v>
       </c>
       <c r="G18" s="4">
         <v>0</v>
       </c>
       <c r="H18" s="6" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/03/24 08:17:34</v>
+        <v>2026/07/22 15:36:02</v>
       </c>
       <c r="I18" s="4">
         <v>0</v>
@@ -1064,14 +1085,14 @@
       <c r="E19" s="5"/>
       <c r="F19" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/03/24 08:17:34</v>
+        <v>2026/07/22 15:36:02</v>
       </c>
       <c r="G19" s="4">
         <v>0</v>
       </c>
       <c r="H19" s="6" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/03/24 08:17:34</v>
+        <v>2026/07/22 15:36:02</v>
       </c>
       <c r="I19" s="4">
         <v>0</v>
@@ -1091,14 +1112,14 @@
       <c r="E20" s="5"/>
       <c r="F20" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/03/24 08:17:34</v>
+        <v>2026/07/22 15:36:02</v>
       </c>
       <c r="G20" s="4">
         <v>0</v>
       </c>
       <c r="H20" s="6" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/03/24 08:17:34</v>
+        <v>2026/07/22 15:36:02</v>
       </c>
       <c r="I20" s="4">
         <v>0</v>
@@ -1118,14 +1139,14 @@
       <c r="E21" s="5"/>
       <c r="F21" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/03/24 08:17:34</v>
+        <v>2026/07/22 15:36:02</v>
       </c>
       <c r="G21" s="4">
         <v>0</v>
       </c>
       <c r="H21" s="6" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/03/24 08:17:34</v>
+        <v>2026/07/22 15:36:02</v>
       </c>
       <c r="I21" s="4">
         <v>0</v>
@@ -1145,14 +1166,14 @@
       <c r="E22" s="5"/>
       <c r="F22" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/03/24 08:17:34</v>
+        <v>2026/07/22 15:36:02</v>
       </c>
       <c r="G22" s="4">
         <v>0</v>
       </c>
       <c r="H22" s="6" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/03/24 08:17:34</v>
+        <v>2026/07/22 15:36:02</v>
       </c>
       <c r="I22" s="4">
         <v>0</v>
@@ -1172,14 +1193,14 @@
       <c r="E23" s="5"/>
       <c r="F23" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/03/24 08:17:34</v>
+        <v>2026/07/22 15:36:02</v>
       </c>
       <c r="G23" s="4">
         <v>0</v>
       </c>
       <c r="H23" s="6" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/03/24 08:17:34</v>
+        <v>2026/07/22 15:36:02</v>
       </c>
       <c r="I23" s="4">
         <v>0</v>
@@ -1199,14 +1220,14 @@
       <c r="E24" s="5"/>
       <c r="F24" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/03/24 08:17:34</v>
+        <v>2026/07/22 15:36:02</v>
       </c>
       <c r="G24" s="4">
         <v>0</v>
       </c>
       <c r="H24" s="6" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/03/24 08:17:34</v>
+        <v>2026/07/22 15:36:02</v>
       </c>
       <c r="I24" s="4">
         <v>0</v>
@@ -1226,14 +1247,14 @@
       <c r="E25" s="5"/>
       <c r="F25" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/03/24 08:17:34</v>
+        <v>2026/07/22 15:36:02</v>
       </c>
       <c r="G25" s="4">
         <v>0</v>
       </c>
       <c r="H25" s="6" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/03/24 08:17:34</v>
+        <v>2026/07/22 15:36:02</v>
       </c>
       <c r="I25" s="4">
         <v>0</v>
@@ -1253,16 +1274,74 @@
       <c r="E26" s="5"/>
       <c r="F26" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/03/24 08:17:34</v>
+        <v>2026/07/22 15:36:02</v>
       </c>
       <c r="G26" s="4">
         <v>0</v>
       </c>
       <c r="H26" s="6" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/03/24 08:17:34</v>
+        <v>2026/07/22 15:36:02</v>
       </c>
       <c r="I26" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
+      <c r="A27" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D27" s="4">
+        <v>1</v>
+      </c>
+      <c r="E27" s="5"/>
+      <c r="F27" s="6" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/07/22 15:36:02</v>
+      </c>
+      <c r="G27" s="4">
+        <v>0</v>
+      </c>
+      <c r="H27" s="6" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>2026/07/22 15:36:02</v>
+      </c>
+      <c r="I27" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
+      <c r="A28" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D28" s="4">
+        <v>2</v>
+      </c>
+      <c r="E28" s="5"/>
+      <c r="F28" s="6" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/07/22 15:36:02</v>
+      </c>
+      <c r="G28" s="4">
+        <v>0</v>
+      </c>
+      <c r="H28" s="6" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>2026/07/22 15:36:02</v>
+      </c>
+      <c r="I28" s="4">
         <v>0</v>
       </c>
     </row>

--- a/.schema/MSY_KBN_VAL.xlsx
+++ b/.schema/MSY_KBN_VAL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KTC0966\git\sample\.schema\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t_fuk\git\sample\.schema\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24F00C45-A58D-46D0-A12F-6C0EF344875A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{395341B4-423F-42CD-BFDD-8D154E51816E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EMARF.MSY_KBN_VAL" sheetId="1" r:id="rId1"/>
@@ -623,14 +623,14 @@
       <c r="E3" s="5"/>
       <c r="F3" s="6" t="str">
         <f t="shared" ref="F3:F28" ca="1" si="0">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
-        <v>2026/07/22 15:36:02</v>
+        <v>2026/08/16 10:57:41</v>
       </c>
       <c r="G3" s="4">
         <v>0</v>
       </c>
       <c r="H3" s="6" t="str">
         <f t="shared" ref="H3:H28" ca="1" si="1">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
-        <v>2026/07/22 15:36:02</v>
+        <v>2026/08/16 10:57:41</v>
       </c>
       <c r="I3" s="4">
         <v>0</v>
@@ -652,14 +652,14 @@
       <c r="E4" s="5"/>
       <c r="F4" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/07/22 15:36:02</v>
+        <v>2026/08/16 10:57:41</v>
       </c>
       <c r="G4" s="4">
         <v>0</v>
       </c>
       <c r="H4" s="6" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/07/22 15:36:02</v>
+        <v>2026/08/16 10:57:41</v>
       </c>
       <c r="I4" s="4">
         <v>0</v>
@@ -681,14 +681,14 @@
       <c r="E5" s="5"/>
       <c r="F5" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/07/22 15:36:02</v>
+        <v>2026/08/16 10:57:41</v>
       </c>
       <c r="G5" s="4">
         <v>0</v>
       </c>
       <c r="H5" s="6" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/07/22 15:36:02</v>
+        <v>2026/08/16 10:57:41</v>
       </c>
       <c r="I5" s="4">
         <v>0</v>
@@ -710,14 +710,14 @@
       <c r="E6" s="5"/>
       <c r="F6" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/07/22 15:36:02</v>
+        <v>2026/08/16 10:57:41</v>
       </c>
       <c r="G6" s="4">
         <v>0</v>
       </c>
       <c r="H6" s="6" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/07/22 15:36:02</v>
+        <v>2026/08/16 10:57:41</v>
       </c>
       <c r="I6" s="4">
         <v>0</v>
@@ -739,14 +739,14 @@
       <c r="E7" s="5"/>
       <c r="F7" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/07/22 15:36:02</v>
+        <v>2026/08/16 10:57:41</v>
       </c>
       <c r="G7" s="4">
         <v>0</v>
       </c>
       <c r="H7" s="6" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/07/22 15:36:02</v>
+        <v>2026/08/16 10:57:41</v>
       </c>
       <c r="I7" s="4">
         <v>0</v>
@@ -768,14 +768,14 @@
       <c r="E8" s="5"/>
       <c r="F8" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/07/22 15:36:02</v>
+        <v>2026/08/16 10:57:41</v>
       </c>
       <c r="G8" s="4">
         <v>0</v>
       </c>
       <c r="H8" s="6" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/07/22 15:36:02</v>
+        <v>2026/08/16 10:57:41</v>
       </c>
       <c r="I8" s="4">
         <v>0</v>
@@ -797,14 +797,14 @@
       <c r="E9" s="5"/>
       <c r="F9" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/07/22 15:36:02</v>
+        <v>2026/08/16 10:57:41</v>
       </c>
       <c r="G9" s="4">
         <v>0</v>
       </c>
       <c r="H9" s="6" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/07/22 15:36:02</v>
+        <v>2026/08/16 10:57:41</v>
       </c>
       <c r="I9" s="4">
         <v>0</v>
@@ -826,14 +826,14 @@
       <c r="E10" s="5"/>
       <c r="F10" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/07/22 15:36:02</v>
+        <v>2026/08/16 10:57:41</v>
       </c>
       <c r="G10" s="4">
         <v>0</v>
       </c>
       <c r="H10" s="6" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/07/22 15:36:02</v>
+        <v>2026/08/16 10:57:41</v>
       </c>
       <c r="I10" s="4">
         <v>0</v>
@@ -855,14 +855,14 @@
       <c r="E11" s="5"/>
       <c r="F11" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/07/22 15:36:02</v>
+        <v>2026/08/16 10:57:41</v>
       </c>
       <c r="G11" s="4">
         <v>0</v>
       </c>
       <c r="H11" s="6" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/07/22 15:36:02</v>
+        <v>2026/08/16 10:57:41</v>
       </c>
       <c r="I11" s="4">
         <v>0</v>
@@ -884,14 +884,14 @@
       <c r="E12" s="5"/>
       <c r="F12" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/07/22 15:36:02</v>
+        <v>2026/08/16 10:57:41</v>
       </c>
       <c r="G12" s="4">
         <v>0</v>
       </c>
       <c r="H12" s="6" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/07/22 15:36:02</v>
+        <v>2026/08/16 10:57:41</v>
       </c>
       <c r="I12" s="4">
         <v>0</v>
@@ -913,14 +913,14 @@
       <c r="E13" s="5"/>
       <c r="F13" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/07/22 15:36:02</v>
+        <v>2026/08/16 10:57:41</v>
       </c>
       <c r="G13" s="4">
         <v>0</v>
       </c>
       <c r="H13" s="6" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/07/22 15:36:02</v>
+        <v>2026/08/16 10:57:41</v>
       </c>
       <c r="I13" s="4">
         <v>0</v>
@@ -942,14 +942,14 @@
       <c r="E14" s="5"/>
       <c r="F14" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/07/22 15:36:02</v>
+        <v>2026/08/16 10:57:41</v>
       </c>
       <c r="G14" s="4">
         <v>0</v>
       </c>
       <c r="H14" s="6" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/07/22 15:36:02</v>
+        <v>2026/08/16 10:57:41</v>
       </c>
       <c r="I14" s="4">
         <v>0</v>
@@ -971,14 +971,14 @@
       <c r="E15" s="5"/>
       <c r="F15" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/07/22 15:36:02</v>
+        <v>2026/08/16 10:57:41</v>
       </c>
       <c r="G15" s="4">
         <v>0</v>
       </c>
       <c r="H15" s="6" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/07/22 15:36:02</v>
+        <v>2026/08/16 10:57:41</v>
       </c>
       <c r="I15" s="4">
         <v>0</v>
@@ -1000,14 +1000,14 @@
       <c r="E16" s="5"/>
       <c r="F16" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/07/22 15:36:02</v>
+        <v>2026/08/16 10:57:41</v>
       </c>
       <c r="G16" s="4">
         <v>0</v>
       </c>
       <c r="H16" s="6" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/07/22 15:36:02</v>
+        <v>2026/08/16 10:57:41</v>
       </c>
       <c r="I16" s="4">
         <v>0</v>
@@ -1029,14 +1029,14 @@
       <c r="E17" s="5"/>
       <c r="F17" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/07/22 15:36:02</v>
+        <v>2026/08/16 10:57:41</v>
       </c>
       <c r="G17" s="4">
         <v>0</v>
       </c>
       <c r="H17" s="6" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/07/22 15:36:02</v>
+        <v>2026/08/16 10:57:41</v>
       </c>
       <c r="I17" s="4">
         <v>0</v>
@@ -1058,14 +1058,14 @@
       <c r="E18" s="5"/>
       <c r="F18" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/07/22 15:36:02</v>
+        <v>2026/08/16 10:57:41</v>
       </c>
       <c r="G18" s="4">
         <v>0</v>
       </c>
       <c r="H18" s="6" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/07/22 15:36:02</v>
+        <v>2026/08/16 10:57:41</v>
       </c>
       <c r="I18" s="4">
         <v>0</v>
@@ -1085,14 +1085,14 @@
       <c r="E19" s="5"/>
       <c r="F19" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/07/22 15:36:02</v>
+        <v>2026/08/16 10:57:41</v>
       </c>
       <c r="G19" s="4">
         <v>0</v>
       </c>
       <c r="H19" s="6" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/07/22 15:36:02</v>
+        <v>2026/08/16 10:57:41</v>
       </c>
       <c r="I19" s="4">
         <v>0</v>
@@ -1112,14 +1112,14 @@
       <c r="E20" s="5"/>
       <c r="F20" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/07/22 15:36:02</v>
+        <v>2026/08/16 10:57:41</v>
       </c>
       <c r="G20" s="4">
         <v>0</v>
       </c>
       <c r="H20" s="6" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/07/22 15:36:02</v>
+        <v>2026/08/16 10:57:41</v>
       </c>
       <c r="I20" s="4">
         <v>0</v>
@@ -1139,14 +1139,14 @@
       <c r="E21" s="5"/>
       <c r="F21" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/07/22 15:36:02</v>
+        <v>2026/08/16 10:57:41</v>
       </c>
       <c r="G21" s="4">
         <v>0</v>
       </c>
       <c r="H21" s="6" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/07/22 15:36:02</v>
+        <v>2026/08/16 10:57:41</v>
       </c>
       <c r="I21" s="4">
         <v>0</v>
@@ -1166,14 +1166,14 @@
       <c r="E22" s="5"/>
       <c r="F22" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/07/22 15:36:02</v>
+        <v>2026/08/16 10:57:41</v>
       </c>
       <c r="G22" s="4">
         <v>0</v>
       </c>
       <c r="H22" s="6" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/07/22 15:36:02</v>
+        <v>2026/08/16 10:57:41</v>
       </c>
       <c r="I22" s="4">
         <v>0</v>
@@ -1193,14 +1193,14 @@
       <c r="E23" s="5"/>
       <c r="F23" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/07/22 15:36:02</v>
+        <v>2026/08/16 10:57:41</v>
       </c>
       <c r="G23" s="4">
         <v>0</v>
       </c>
       <c r="H23" s="6" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/07/22 15:36:02</v>
+        <v>2026/08/16 10:57:41</v>
       </c>
       <c r="I23" s="4">
         <v>0</v>
@@ -1220,14 +1220,14 @@
       <c r="E24" s="5"/>
       <c r="F24" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/07/22 15:36:02</v>
+        <v>2026/08/16 10:57:41</v>
       </c>
       <c r="G24" s="4">
         <v>0</v>
       </c>
       <c r="H24" s="6" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/07/22 15:36:02</v>
+        <v>2026/08/16 10:57:41</v>
       </c>
       <c r="I24" s="4">
         <v>0</v>
@@ -1247,14 +1247,14 @@
       <c r="E25" s="5"/>
       <c r="F25" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/07/22 15:36:02</v>
+        <v>2026/08/16 10:57:41</v>
       </c>
       <c r="G25" s="4">
         <v>0</v>
       </c>
       <c r="H25" s="6" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/07/22 15:36:02</v>
+        <v>2026/08/16 10:57:41</v>
       </c>
       <c r="I25" s="4">
         <v>0</v>
@@ -1274,14 +1274,14 @@
       <c r="E26" s="5"/>
       <c r="F26" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/07/22 15:36:02</v>
+        <v>2026/08/16 10:57:41</v>
       </c>
       <c r="G26" s="4">
         <v>0</v>
       </c>
       <c r="H26" s="6" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/07/22 15:36:02</v>
+        <v>2026/08/16 10:57:41</v>
       </c>
       <c r="I26" s="4">
         <v>0</v>
@@ -1303,14 +1303,14 @@
       <c r="E27" s="5"/>
       <c r="F27" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/07/22 15:36:02</v>
+        <v>2026/08/16 10:57:41</v>
       </c>
       <c r="G27" s="4">
         <v>0</v>
       </c>
       <c r="H27" s="6" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/07/22 15:36:02</v>
+        <v>2026/08/16 10:57:41</v>
       </c>
       <c r="I27" s="4">
         <v>0</v>
@@ -1332,14 +1332,14 @@
       <c r="E28" s="5"/>
       <c r="F28" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/07/22 15:36:02</v>
+        <v>2026/08/16 10:57:41</v>
       </c>
       <c r="G28" s="4">
         <v>0</v>
       </c>
       <c r="H28" s="6" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/07/22 15:36:02</v>
+        <v>2026/08/16 10:57:41</v>
       </c>
       <c r="I28" s="4">
         <v>0</v>
